--- a/LaRoja/LaRoja.xlsx
+++ b/LaRoja/LaRoja.xlsx
@@ -21472,7 +21472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21568,90 +21568,60 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>NY Sprint 2</t>
+          <t>Tower Sprint points</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Manhattan Sprint</t>
+          <t>Castle Park Sprint points</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Manhattan Sprint Reverse</t>
+          <t>Alley Sprint points</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Tower Sprint points</t>
+          <t>Stoneway Sprint points</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Castle Park Sprint points</t>
+          <t>Stoneway Sprint Reverse points</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Alley Sprint points</t>
+          <t>Acropolis Sprint points</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Stoneway Sprint points</t>
+          <t>Acropolis Sprint Reverse points</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Stoneway Sprint Reverse points</t>
+          <t>Sasquatch Sprint points</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Acropolis Sprint points</t>
+          <t>Sasquatch Sprint Reverse points</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Acropolis Sprint Reverse points</t>
+          <t>Woodland Sprint points</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Sasquatch Sprint points</t>
+          <t>Woodland Sprint Reverse points</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Sasquatch Sprint Reverse points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Woodland Sprint points</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Woodland Sprint Reverse points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>NY Sprint 2 points</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Manhattan Sprint points</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Manhattan Sprint Reverse points</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>time_offset</t>
         </is>
@@ -21682,7 +21652,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>254</v>
+        <v>204</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -21721,16 +21691,16 @@
         <v>30.934</v>
       </c>
       <c r="S2" t="n">
-        <v>10.716</v>
+        <v>18</v>
       </c>
       <c r="T2" t="n">
-        <v>22.915</v>
+        <v>20</v>
       </c>
       <c r="U2" t="n">
-        <v>24.049</v>
+        <v>20</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
         <v>20</v>
@@ -21739,7 +21709,7 @@
         <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
         <v>20</v>
@@ -21748,34 +21718,16 @@
         <v>20</v>
       </c>
       <c r="AB2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
         <v>20</v>
       </c>
-      <c r="AD2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4980720</v>
+        <v>2425872</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -21784,114 +21736,96 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t>Alexandre Lagrange [EVO]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>26.158</v>
+        <v>28.4</v>
       </c>
       <c r="I3" t="n">
-        <v>16.975</v>
+        <v>15.265</v>
       </c>
       <c r="J3" t="n">
-        <v>30.658</v>
+        <v>28.066</v>
       </c>
       <c r="K3" t="n">
-        <v>36.009</v>
+        <v>31.839</v>
       </c>
       <c r="L3" t="n">
-        <v>29.765</v>
+        <v>29.768</v>
       </c>
       <c r="M3" t="n">
-        <v>33.493</v>
+        <v>31.498</v>
       </c>
       <c r="N3" t="n">
-        <v>36.307</v>
+        <v>37.966</v>
       </c>
       <c r="O3" t="n">
-        <v>27.605</v>
+        <v>25.401</v>
       </c>
       <c r="P3" t="n">
-        <v>26.079</v>
+        <v>26.097</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.204</v>
+        <v>34.197</v>
       </c>
       <c r="R3" t="n">
-        <v>34.057</v>
+        <v>34.86</v>
       </c>
       <c r="S3" t="n">
-        <v>11.261</v>
+        <v>12</v>
       </c>
       <c r="T3" t="n">
-        <v>22.999</v>
+        <v>18</v>
       </c>
       <c r="U3" t="n">
-        <v>23.856</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB3" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>14</v>
       </c>
-      <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2425872</v>
+        <v>4980720</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -21900,110 +21834,92 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alexandre Lagrange [EVO]</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>28.4</v>
+        <v>26.158</v>
       </c>
       <c r="I4" t="n">
-        <v>15.265</v>
+        <v>16.975</v>
       </c>
       <c r="J4" t="n">
-        <v>28.066</v>
+        <v>30.658</v>
       </c>
       <c r="K4" t="n">
-        <v>31.839</v>
+        <v>36.009</v>
       </c>
       <c r="L4" t="n">
-        <v>29.768</v>
+        <v>29.765</v>
       </c>
       <c r="M4" t="n">
-        <v>31.498</v>
+        <v>33.493</v>
       </c>
       <c r="N4" t="n">
-        <v>37.966</v>
+        <v>36.307</v>
       </c>
       <c r="O4" t="n">
-        <v>25.401</v>
+        <v>27.605</v>
       </c>
       <c r="P4" t="n">
-        <v>26.097</v>
+        <v>26.079</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.197</v>
+        <v>31.204</v>
       </c>
       <c r="R4" t="n">
-        <v>34.86</v>
+        <v>34.057</v>
       </c>
       <c r="S4" t="n">
-        <v>10.998</v>
+        <v>20</v>
       </c>
       <c r="T4" t="n">
-        <v>24.136</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>26.268</v>
+        <v>5</v>
       </c>
       <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="n">
         <v>12</v>
       </c>
-      <c r="W4" t="n">
-        <v>18</v>
-      </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
         <v>10</v>
       </c>
       <c r="AA4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AC4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -22030,7 +21946,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
@@ -22069,57 +21985,39 @@
         <v>35.306</v>
       </c>
       <c r="S5" t="n">
-        <v>10.568</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>23.756</v>
+        <v>9</v>
       </c>
       <c r="U5" t="n">
-        <v>24.833</v>
+        <v>8</v>
       </c>
       <c r="V5" t="n">
+        <v>16</v>
+      </c>
+      <c r="W5" t="n">
+        <v>18</v>
+      </c>
+      <c r="X5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB5" t="n">
         <v>7</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>9</v>
       </c>
-      <c r="X5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -22146,7 +22044,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -22185,57 +22083,39 @@
         <v>38.117</v>
       </c>
       <c r="S6" t="n">
-        <v>10.37</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>23.481</v>
+        <v>12</v>
       </c>
       <c r="U6" t="n">
-        <v>25.36</v>
+        <v>18</v>
       </c>
       <c r="V6" t="n">
+        <v>14</v>
+      </c>
+      <c r="W6" t="n">
         <v>6</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>12</v>
       </c>
-      <c r="X6" t="n">
-        <v>18</v>
-      </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA6" t="n">
         <v>6</v>
       </c>
-      <c r="AA6" t="n">
-        <v>12</v>
-      </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF6" t="n">
         <v>4</v>
       </c>
-      <c r="AG6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -22262,7 +22142,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -22301,57 +22181,39 @@
         <v>37.384</v>
       </c>
       <c r="S7" t="n">
-        <v>10.799</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>22.847</v>
+        <v>14</v>
       </c>
       <c r="U7" t="n">
-        <v>25.899</v>
+        <v>14</v>
       </c>
       <c r="V7" t="n">
+        <v>12</v>
+      </c>
+      <c r="W7" t="n">
         <v>8</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="n">
         <v>14</v>
       </c>
-      <c r="X7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8</v>
-      </c>
       <c r="AA7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF7" t="n">
         <v>5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -22378,7 +22240,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -22417,57 +22279,39 @@
         <v>31.7</v>
       </c>
       <c r="S8" t="n">
-        <v>10.258</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>24.571</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
-        <v>26.116</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z8" t="n">
         <v>4</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB8" t="n">
         <v>5</v>
       </c>
-      <c r="X8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>20</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD8" t="n">
         <v>18</v>
       </c>
-      <c r="AE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -22490,7 +22334,7 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -22529,57 +22373,39 @@
         <v>37.279</v>
       </c>
       <c r="S9" t="n">
-        <v>10.959</v>
+        <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>23.32</v>
+        <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>30.358</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
         <v>9</v>
       </c>
       <c r="W9" t="n">
+        <v>16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
         <v>8</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC9" t="n">
         <v>6</v>
       </c>
-      <c r="Y9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -22606,7 +22432,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
@@ -22645,61 +22471,43 @@
         <v>36.908</v>
       </c>
       <c r="S10" t="n">
-        <v>10.916</v>
+        <v>14</v>
       </c>
       <c r="T10" t="n">
-        <v>25.317</v>
+        <v>16</v>
       </c>
       <c r="U10" t="n">
-        <v>25.811</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" t="n">
         <v>16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4</v>
       </c>
       <c r="AC10" t="n">
         <v>8</v>
       </c>
-      <c r="AD10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2213032</v>
+        <v>394612</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -22708,12 +22516,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ben Howell (EVO)</t>
+          <t>Mark Redfern [EVO]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -22722,100 +22530,82 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="G11" t="n">
         <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>28.956</v>
+        <v>29.382</v>
       </c>
       <c r="I11" t="n">
-        <v>16.598</v>
+        <v>16.373</v>
       </c>
       <c r="J11" t="n">
-        <v>27.186</v>
+        <v>25.231</v>
       </c>
       <c r="K11" t="n">
-        <v>39.029</v>
+        <v>36.667</v>
       </c>
       <c r="L11" t="n">
-        <v>34.182</v>
+        <v>39.885</v>
       </c>
       <c r="M11" t="n">
-        <v>37.156</v>
+        <v>33.501</v>
       </c>
       <c r="N11" t="n">
-        <v>36.455</v>
+        <v>40.135</v>
       </c>
       <c r="O11" t="n">
-        <v>29.512</v>
+        <v>27.632</v>
       </c>
       <c r="P11" t="n">
-        <v>30.411</v>
+        <v>27.692</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.954</v>
+        <v>34.161</v>
       </c>
       <c r="R11" t="n">
-        <v>35.12</v>
+        <v>37.218</v>
       </c>
       <c r="S11" t="n">
-        <v>10.794</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>23.294</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>24.46</v>
+        <v>16</v>
       </c>
       <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA11" t="n">
         <v>10</v>
-      </c>
-      <c r="W11" t="n">
-        <v>6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>394612</v>
+        <v>1511742</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -22829,109 +22619,91 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mark Redfern [EVO]</t>
+          <t>Mark Hayes [PWCC]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>29.382</v>
+        <v>28.199</v>
       </c>
       <c r="I12" t="n">
-        <v>16.373</v>
+        <v>15.937</v>
       </c>
       <c r="J12" t="n">
-        <v>25.231</v>
+        <v>27.643</v>
       </c>
       <c r="K12" t="n">
-        <v>36.667</v>
+        <v>38.148</v>
       </c>
       <c r="L12" t="n">
-        <v>39.885</v>
+        <v>30.209</v>
       </c>
       <c r="M12" t="n">
-        <v>33.501</v>
+        <v>35.325</v>
       </c>
       <c r="N12" t="n">
-        <v>40.135</v>
+        <v>38.259</v>
       </c>
       <c r="O12" t="n">
-        <v>27.632</v>
+        <v>29.658</v>
       </c>
       <c r="P12" t="n">
-        <v>27.692</v>
+        <v>32.018</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.161</v>
+        <v>37.541</v>
       </c>
       <c r="R12" t="n">
-        <v>37.218</v>
+        <v>35.185</v>
       </c>
       <c r="S12" t="n">
-        <v>11.428</v>
+        <v>16</v>
       </c>
       <c r="T12" t="n">
-        <v>24.821</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>26.526</v>
+        <v>10</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
         <v>4</v>
       </c>
-      <c r="AA12" t="n">
-        <v>9</v>
-      </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
         <v>10</v>
       </c>
-      <c r="AE12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1511742</v>
+        <v>2213032</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -22940,110 +22712,92 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mark Hayes [PWCC]</t>
+          <t>Ben Howell (EVO)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
         <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>28.199</v>
+        <v>28.956</v>
       </c>
       <c r="I13" t="n">
-        <v>15.937</v>
+        <v>16.598</v>
       </c>
       <c r="J13" t="n">
-        <v>27.643</v>
+        <v>27.186</v>
       </c>
       <c r="K13" t="n">
-        <v>38.148</v>
+        <v>39.029</v>
       </c>
       <c r="L13" t="n">
-        <v>30.209</v>
+        <v>34.182</v>
       </c>
       <c r="M13" t="n">
-        <v>35.325</v>
+        <v>37.156</v>
       </c>
       <c r="N13" t="n">
-        <v>38.259</v>
+        <v>36.455</v>
       </c>
       <c r="O13" t="n">
-        <v>29.658</v>
+        <v>29.512</v>
       </c>
       <c r="P13" t="n">
-        <v>32.018</v>
+        <v>30.411</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.541</v>
+        <v>35.954</v>
       </c>
       <c r="R13" t="n">
-        <v>35.185</v>
+        <v>35.12</v>
       </c>
       <c r="S13" t="n">
-        <v>11.489</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>25.336</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>26.817</v>
+        <v>12</v>
       </c>
       <c r="V13" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
         <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ13" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -23070,7 +22824,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -23109,28 +22863,28 @@
         <v>31.35</v>
       </c>
       <c r="S14" t="n">
-        <v>11.001</v>
+        <v>18</v>
       </c>
       <c r="T14" t="n">
-        <v>25.311</v>
+        <v>16</v>
       </c>
       <c r="U14" t="n">
-        <v>27.148</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X14" t="n">
         <v>18</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
         <v>18</v>
@@ -23139,27 +22893,9 @@
         <v>18</v>
       </c>
       <c r="AC14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF14" t="n">
         <v>20</v>
       </c>
-      <c r="AG14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -23186,7 +22922,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
@@ -23225,57 +22961,39 @@
         <v>32.407</v>
       </c>
       <c r="S15" t="n">
-        <v>11.519</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>24.717</v>
+        <v>20</v>
       </c>
       <c r="U15" t="n">
-        <v>27.86</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB15" t="n">
         <v>20</v>
       </c>
-      <c r="X15" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10</v>
-      </c>
       <c r="AC15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF15" t="n">
         <v>16</v>
       </c>
-      <c r="AG15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -23298,7 +23016,7 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="G16" t="n">
         <v>3</v>
@@ -23337,61 +23055,43 @@
         <v>36.544</v>
       </c>
       <c r="S16" t="n">
-        <v>10.418</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>27.816</v>
+        <v>8</v>
       </c>
       <c r="U16" t="n">
-        <v>28.645</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AB16" t="n">
         <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF16" t="n">
         <v>8</v>
       </c>
-      <c r="AG16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5158243</v>
+        <v>1236596</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -23400,114 +23100,96 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Martin Chambers [sisu]</t>
+          <t>Neil Rogers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>33.444</v>
+        <v>28.914</v>
       </c>
       <c r="I17" t="n">
-        <v>19.602</v>
+        <v>15.733</v>
       </c>
       <c r="J17" t="n">
-        <v>30.106</v>
+        <v>30.608</v>
       </c>
       <c r="K17" t="n">
-        <v>36.802</v>
+        <v>37.723</v>
       </c>
       <c r="L17" t="n">
-        <v>31.073</v>
+        <v>28.369</v>
       </c>
       <c r="M17" t="n">
-        <v>33.132</v>
+        <v>33.333</v>
       </c>
       <c r="N17" t="n">
-        <v>34.339</v>
+        <v>31.705</v>
       </c>
       <c r="O17" t="n">
-        <v>24.366</v>
+        <v>24.564</v>
       </c>
       <c r="P17" t="n">
-        <v>29.68</v>
+        <v>25.901</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.716</v>
+        <v>34.945</v>
       </c>
       <c r="R17" t="n">
-        <v>32.045</v>
+        <v>32.475</v>
       </c>
       <c r="S17" t="n">
-        <v>11.083</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>25.759</v>
+        <v>14</v>
       </c>
       <c r="U17" t="n">
-        <v>28.084</v>
+        <v>10</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC17" t="n">
         <v>14</v>
       </c>
-      <c r="Y17" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>260262</v>
+        <v>5158243</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -23521,109 +23203,91 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>Martin Chambers [sisu]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>32.022</v>
+        <v>33.444</v>
       </c>
       <c r="I18" t="n">
-        <v>20.003</v>
+        <v>19.602</v>
       </c>
       <c r="J18" t="n">
-        <v>34.536</v>
+        <v>30.106</v>
       </c>
       <c r="K18" t="n">
-        <v>38.469</v>
+        <v>36.802</v>
       </c>
       <c r="L18" t="n">
-        <v>31.971</v>
+        <v>31.073</v>
       </c>
       <c r="M18" t="n">
-        <v>34.385</v>
+        <v>33.132</v>
       </c>
       <c r="N18" t="n">
-        <v>30.655</v>
+        <v>34.339</v>
       </c>
       <c r="O18" t="n">
-        <v>21.282</v>
+        <v>24.366</v>
       </c>
       <c r="P18" t="n">
-        <v>23.533</v>
+        <v>29.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>33.864</v>
+        <v>34.716</v>
       </c>
       <c r="R18" t="n">
-        <v>33.107</v>
+        <v>32.045</v>
       </c>
       <c r="S18" t="n">
-        <v>11.672</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>27.238</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
-        <v>28.632</v>
+        <v>14</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="W18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ18" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1236596</v>
+        <v>260262</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -23632,110 +23296,92 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
+          <t>Greg SHED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="G19" t="n">
         <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>28.914</v>
+        <v>32.022</v>
       </c>
       <c r="I19" t="n">
-        <v>15.733</v>
+        <v>20.003</v>
       </c>
       <c r="J19" t="n">
-        <v>30.608</v>
+        <v>34.536</v>
       </c>
       <c r="K19" t="n">
-        <v>37.723</v>
+        <v>38.469</v>
       </c>
       <c r="L19" t="n">
-        <v>28.369</v>
+        <v>31.971</v>
       </c>
       <c r="M19" t="n">
-        <v>33.333</v>
+        <v>34.385</v>
       </c>
       <c r="N19" t="n">
-        <v>31.705</v>
+        <v>30.655</v>
       </c>
       <c r="O19" t="n">
-        <v>24.564</v>
+        <v>21.282</v>
       </c>
       <c r="P19" t="n">
-        <v>25.901</v>
+        <v>23.533</v>
       </c>
       <c r="Q19" t="n">
-        <v>34.945</v>
+        <v>33.864</v>
       </c>
       <c r="R19" t="n">
-        <v>32.475</v>
+        <v>33.107</v>
       </c>
       <c r="S19" t="n">
-        <v>11.872</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>27.549</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>33.328</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
         <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="n">
         <v>16</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD19" t="n">
         <v>12</v>
       </c>
-      <c r="AE19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -23762,7 +23408,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="G20" t="n">
         <v>3</v>
@@ -23801,28 +23447,28 @@
         <v>34.582</v>
       </c>
       <c r="S20" t="n">
-        <v>11.736</v>
+        <v>20</v>
       </c>
       <c r="T20" t="n">
-        <v>26.567</v>
+        <v>10</v>
       </c>
       <c r="U20" t="n">
-        <v>29.316</v>
+        <v>16</v>
       </c>
       <c r="V20" t="n">
+        <v>10</v>
+      </c>
+      <c r="W20" t="n">
         <v>20</v>
       </c>
-      <c r="W20" t="n">
-        <v>10</v>
-      </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
         <v>7</v>
@@ -23831,31 +23477,13 @@
         <v>6</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF20" t="n">
         <v>9</v>
       </c>
-      <c r="AG20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3785513</v>
+        <v>2881429</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -23864,114 +23492,96 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Chris Beardsell (TNP)</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="G21" t="n">
         <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>28.623</v>
+        <v>26.874</v>
       </c>
       <c r="I21" t="n">
-        <v>17.161</v>
+        <v>14.42</v>
       </c>
       <c r="J21" t="n">
-        <v>31.254</v>
+        <v>30.513</v>
       </c>
       <c r="K21" t="n">
-        <v>32.387</v>
+        <v>39.698</v>
       </c>
       <c r="L21" t="n">
-        <v>28.49</v>
+        <v>29.057</v>
       </c>
       <c r="M21" t="n">
-        <v>33.222</v>
+        <v>35.112</v>
       </c>
       <c r="N21" t="n">
-        <v>43.45</v>
+        <v>37.547</v>
       </c>
       <c r="O21" t="n">
-        <v>30.421</v>
+        <v>29.482</v>
       </c>
       <c r="P21" t="n">
-        <v>32.021</v>
+        <v>31.294</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.753</v>
+        <v>37.128</v>
       </c>
       <c r="R21" t="n">
-        <v>40.018</v>
+        <v>34.549</v>
       </c>
       <c r="S21" t="n">
-        <v>10.796</v>
+        <v>16</v>
       </c>
       <c r="T21" t="n">
-        <v>27.557</v>
+        <v>18</v>
       </c>
       <c r="U21" t="n">
-        <v>30.089</v>
+        <v>12</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>12</v>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AB21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2881429</v>
+        <v>3785513</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -23980,110 +23590,92 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Chris Beardsell (TNP)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>26.874</v>
+        <v>28.623</v>
       </c>
       <c r="I22" t="n">
-        <v>14.42</v>
+        <v>17.161</v>
       </c>
       <c r="J22" t="n">
-        <v>30.513</v>
+        <v>31.254</v>
       </c>
       <c r="K22" t="n">
-        <v>39.698</v>
+        <v>32.387</v>
       </c>
       <c r="L22" t="n">
-        <v>29.057</v>
+        <v>28.49</v>
       </c>
       <c r="M22" t="n">
-        <v>35.112</v>
+        <v>33.222</v>
       </c>
       <c r="N22" t="n">
-        <v>37.547</v>
+        <v>43.45</v>
       </c>
       <c r="O22" t="n">
-        <v>29.482</v>
+        <v>30.421</v>
       </c>
       <c r="P22" t="n">
-        <v>31.294</v>
+        <v>32.021</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.128</v>
+        <v>37.753</v>
       </c>
       <c r="R22" t="n">
-        <v>34.549</v>
+        <v>40.018</v>
       </c>
       <c r="S22" t="n">
-        <v>11.482</v>
+        <v>10</v>
       </c>
       <c r="T22" t="n">
-        <v>29.1</v>
+        <v>12</v>
       </c>
       <c r="U22" t="n">
-        <v>32.516</v>
+        <v>9</v>
       </c>
       <c r="V22" t="n">
+        <v>20</v>
+      </c>
+      <c r="W22" t="n">
         <v>16</v>
       </c>
-      <c r="W22" t="n">
-        <v>18</v>
-      </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH22" t="n">
         <v>5</v>
       </c>
-      <c r="AI22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -24110,7 +23702,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
@@ -24149,57 +23741,39 @@
         <v>37.231</v>
       </c>
       <c r="S23" t="n">
-        <v>11.599</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>29.033</v>
+        <v>9</v>
       </c>
       <c r="U23" t="n">
-        <v>31.216</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
         <v>8</v>
       </c>
       <c r="W23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" t="n">
         <v>9</v>
       </c>
-      <c r="X23" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB23" t="n">
         <v>8</v>
       </c>
-      <c r="Z23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9</v>
-      </c>
       <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF23" t="n">
         <v>7</v>
       </c>
-      <c r="AG23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -24226,7 +23800,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
@@ -24265,57 +23839,39 @@
         <v>37.601</v>
       </c>
       <c r="S24" t="n">
-        <v>11.626</v>
+        <v>14</v>
       </c>
       <c r="T24" t="n">
-        <v>27.863</v>
+        <v>7</v>
       </c>
       <c r="U24" t="n">
-        <v>29.763</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="n">
         <v>8</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>6</v>
       </c>
-      <c r="Z24" t="n">
-        <v>5</v>
-      </c>
       <c r="AA24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC24" t="n">
         <v>6</v>
       </c>
-      <c r="AD24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -24342,7 +23898,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>257</v>
+        <v>210</v>
       </c>
       <c r="G25" t="n">
         <v>3</v>
@@ -24381,19 +23937,19 @@
         <v>30.854</v>
       </c>
       <c r="S25" t="n">
-        <v>11.071</v>
+        <v>20</v>
       </c>
       <c r="T25" t="n">
-        <v>25.721</v>
+        <v>18</v>
       </c>
       <c r="U25" t="n">
-        <v>30.316</v>
+        <v>20</v>
       </c>
       <c r="V25" t="n">
         <v>20</v>
       </c>
       <c r="W25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="X25" t="n">
         <v>20</v>
@@ -24402,40 +23958,22 @@
         <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA25" t="n">
         <v>20</v>
       </c>
       <c r="AB25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC25" t="n">
         <v>20</v>
       </c>
-      <c r="AC25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2297188</v>
+        <v>1379058</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -24449,7 +23987,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Javier (HERC) </t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -24458,96 +23996,78 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>28.246</v>
+        <v>28.191</v>
       </c>
       <c r="I26" t="n">
-        <v>14.3</v>
+        <v>13.958</v>
       </c>
       <c r="J26" t="n">
-        <v>26.957</v>
+        <v>25.5</v>
       </c>
       <c r="K26" t="n">
-        <v>34.569</v>
+        <v>34.196</v>
       </c>
       <c r="L26" t="n">
-        <v>30.304</v>
+        <v>30.968</v>
       </c>
       <c r="M26" t="n">
-        <v>31.56</v>
+        <v>30.693</v>
       </c>
       <c r="N26" t="n">
-        <v>31.872</v>
+        <v>34.144</v>
       </c>
       <c r="O26" t="n">
-        <v>22.659</v>
+        <v>23.774</v>
       </c>
       <c r="P26" t="n">
-        <v>24.401</v>
+        <v>26.355</v>
       </c>
       <c r="Q26" t="n">
-        <v>31.788</v>
+        <v>30.562</v>
       </c>
       <c r="R26" t="n">
-        <v>32.719</v>
+        <v>31.094</v>
       </c>
       <c r="S26" t="n">
-        <v>11.594</v>
+        <v>9</v>
       </c>
       <c r="T26" t="n">
-        <v>25.188</v>
+        <v>20</v>
       </c>
       <c r="U26" t="n">
-        <v>27.588</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W26" t="n">
+        <v>12</v>
+      </c>
+      <c r="X26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" t="n">
         <v>14</v>
-      </c>
-      <c r="X26" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>16</v>
       </c>
       <c r="Z26" t="n">
         <v>14</v>
       </c>
       <c r="AA26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
         <v>16</v>
       </c>
-      <c r="AD26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -24574,7 +24094,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="G27" t="n">
         <v>3</v>
@@ -24613,61 +24133,43 @@
         <v>30.998</v>
       </c>
       <c r="S27" t="n">
-        <v>11.918</v>
+        <v>16</v>
       </c>
       <c r="T27" t="n">
-        <v>27.039</v>
+        <v>16</v>
       </c>
       <c r="U27" t="n">
-        <v>28.36</v>
+        <v>10</v>
       </c>
       <c r="V27" t="n">
+        <v>14</v>
+      </c>
+      <c r="W27" t="n">
+        <v>18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y27" t="n">
         <v>16</v>
       </c>
-      <c r="W27" t="n">
-        <v>16</v>
-      </c>
-      <c r="X27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>14</v>
-      </c>
       <c r="Z27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA27" t="n">
         <v>18</v>
       </c>
-      <c r="AA27" t="n">
-        <v>14</v>
-      </c>
       <c r="AB27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD27" t="n">
         <v>18</v>
       </c>
-      <c r="AE27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1379058</v>
+        <v>2297188</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -24681,7 +24183,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t xml:space="preserve">3 Javier (HERC) </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -24690,100 +24192,82 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="G28" t="n">
         <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>28.191</v>
+        <v>28.246</v>
       </c>
       <c r="I28" t="n">
-        <v>13.958</v>
+        <v>14.3</v>
       </c>
       <c r="J28" t="n">
-        <v>25.5</v>
+        <v>26.957</v>
       </c>
       <c r="K28" t="n">
-        <v>34.196</v>
+        <v>34.569</v>
       </c>
       <c r="L28" t="n">
-        <v>30.968</v>
+        <v>30.304</v>
       </c>
       <c r="M28" t="n">
-        <v>30.693</v>
+        <v>31.56</v>
       </c>
       <c r="N28" t="n">
-        <v>34.144</v>
+        <v>31.872</v>
       </c>
       <c r="O28" t="n">
-        <v>23.774</v>
+        <v>22.659</v>
       </c>
       <c r="P28" t="n">
-        <v>26.355</v>
+        <v>24.401</v>
       </c>
       <c r="Q28" t="n">
-        <v>30.562</v>
+        <v>31.788</v>
       </c>
       <c r="R28" t="n">
-        <v>31.094</v>
+        <v>32.719</v>
       </c>
       <c r="S28" t="n">
-        <v>12.011</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>29.009</v>
+        <v>14</v>
       </c>
       <c r="U28" t="n">
-        <v>30.458</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W28" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="X28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="n">
         <v>18</v>
       </c>
       <c r="Z28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="n">
         <v>12</v>
       </c>
-      <c r="AA28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4698430</v>
+        <v>450573</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -24797,7 +24281,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Maria ( HERC)</t>
+          <t xml:space="preserve">Karin Lamers (HERC - SRT) </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -24806,100 +24290,82 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="G29" t="n">
         <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>26.585</v>
+        <v>28.148</v>
       </c>
       <c r="I29" t="n">
-        <v>14.949</v>
+        <v>15.439</v>
       </c>
       <c r="J29" t="n">
-        <v>28.654</v>
+        <v>27.905</v>
       </c>
       <c r="K29" t="n">
-        <v>37.157</v>
+        <v>40.66</v>
       </c>
       <c r="L29" t="n">
-        <v>31.535</v>
+        <v>33.722</v>
       </c>
       <c r="M29" t="n">
-        <v>38.622</v>
+        <v>34.244</v>
       </c>
       <c r="N29" t="n">
-        <v>35.949</v>
+        <v>36.664</v>
       </c>
       <c r="O29" t="n">
-        <v>27.107</v>
+        <v>25.476</v>
       </c>
       <c r="P29" t="n">
-        <v>27.627</v>
+        <v>26.927</v>
       </c>
       <c r="Q29" t="n">
-        <v>34.38</v>
+        <v>33.363</v>
       </c>
       <c r="R29" t="n">
-        <v>37.388</v>
+        <v>33.531</v>
       </c>
       <c r="S29" t="n">
-        <v>11.445</v>
+        <v>10</v>
       </c>
       <c r="T29" t="n">
-        <v>27.984</v>
+        <v>9</v>
       </c>
       <c r="U29" t="n">
-        <v>29.32</v>
+        <v>12</v>
       </c>
       <c r="V29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
+        <v>9</v>
+      </c>
+      <c r="X29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA29" t="n">
         <v>12</v>
       </c>
-      <c r="X29" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>10</v>
       </c>
-      <c r="AA29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>12</v>
-      </c>
       <c r="AC29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ29" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8033165</v>
+        <v>4698430</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -24913,7 +24379,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Antonia  [HERC]</t>
+          <t>Maria ( HERC)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -24922,100 +24388,82 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="G30" t="n">
         <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>27.002</v>
+        <v>26.585</v>
       </c>
       <c r="I30" t="n">
-        <v>16.817</v>
+        <v>14.949</v>
       </c>
       <c r="J30" t="n">
-        <v>30.24</v>
+        <v>28.654</v>
       </c>
       <c r="K30" t="n">
-        <v>39.277</v>
+        <v>37.157</v>
       </c>
       <c r="L30" t="n">
-        <v>34.838</v>
+        <v>31.535</v>
       </c>
       <c r="M30" t="n">
-        <v>38.838</v>
+        <v>38.622</v>
       </c>
       <c r="N30" t="n">
-        <v>37.318</v>
+        <v>35.949</v>
       </c>
       <c r="O30" t="n">
-        <v>28.878</v>
+        <v>27.107</v>
       </c>
       <c r="P30" t="n">
-        <v>27.918</v>
+        <v>27.627</v>
       </c>
       <c r="Q30" t="n">
-        <v>33.678</v>
+        <v>34.38</v>
       </c>
       <c r="R30" t="n">
-        <v>37.519</v>
+        <v>37.388</v>
       </c>
       <c r="S30" t="n">
-        <v>11.559</v>
+        <v>14</v>
       </c>
       <c r="T30" t="n">
-        <v>25.838</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>27.878</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
         <v>12</v>
       </c>
       <c r="W30" t="n">
+        <v>10</v>
+      </c>
+      <c r="X30" t="n">
         <v>6</v>
       </c>
-      <c r="X30" t="n">
-        <v>5</v>
-      </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ30" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>450573</v>
+        <v>6513233</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -25029,7 +24477,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karin Lamers (HERC - SRT) </t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -25038,100 +24486,82 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="G31" t="n">
         <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>28.148</v>
+        <v>29.122</v>
       </c>
       <c r="I31" t="n">
-        <v>15.439</v>
+        <v>15.3</v>
       </c>
       <c r="J31" t="n">
-        <v>27.905</v>
+        <v>26.618</v>
       </c>
       <c r="K31" t="n">
-        <v>40.66</v>
+        <v>39.203</v>
       </c>
       <c r="L31" t="n">
-        <v>33.722</v>
+        <v>39.061</v>
       </c>
       <c r="M31" t="n">
-        <v>34.244</v>
+        <v>33.348</v>
       </c>
       <c r="N31" t="n">
-        <v>36.664</v>
+        <v>39.508</v>
       </c>
       <c r="O31" t="n">
-        <v>25.476</v>
+        <v>25.4</v>
       </c>
       <c r="P31" t="n">
-        <v>26.927</v>
+        <v>29.134</v>
       </c>
       <c r="Q31" t="n">
-        <v>33.363</v>
+        <v>33.451</v>
       </c>
       <c r="R31" t="n">
-        <v>33.531</v>
+        <v>34.08</v>
       </c>
       <c r="S31" t="n">
-        <v>12.023</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>28.783</v>
+        <v>10</v>
       </c>
       <c r="U31" t="n">
-        <v>31.106</v>
+        <v>16</v>
       </c>
       <c r="V31" t="n">
         <v>10</v>
       </c>
       <c r="W31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ31" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6513233</v>
+        <v>574469</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -25145,7 +24575,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Tracy Aldridge-Jones (HERCULES)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -25154,100 +24584,82 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G32" t="n">
         <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>29.122</v>
+        <v>28.595</v>
       </c>
       <c r="I32" t="n">
-        <v>15.3</v>
+        <v>16.168</v>
       </c>
       <c r="J32" t="n">
-        <v>26.618</v>
+        <v>28.495</v>
       </c>
       <c r="K32" t="n">
-        <v>39.203</v>
+        <v>40.755</v>
       </c>
       <c r="L32" t="n">
-        <v>39.061</v>
+        <v>34.098</v>
       </c>
       <c r="M32" t="n">
-        <v>33.348</v>
+        <v>32.928</v>
       </c>
       <c r="N32" t="n">
-        <v>39.508</v>
+        <v>35.976</v>
       </c>
       <c r="O32" t="n">
-        <v>25.4</v>
+        <v>26.636</v>
       </c>
       <c r="P32" t="n">
-        <v>29.134</v>
+        <v>28.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>33.451</v>
+        <v>38.964</v>
       </c>
       <c r="R32" t="n">
-        <v>34.08</v>
+        <v>31.955</v>
       </c>
       <c r="S32" t="n">
-        <v>11.431</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>30.238</v>
+        <v>7</v>
       </c>
       <c r="U32" t="n">
-        <v>34.889</v>
+        <v>9</v>
       </c>
       <c r="V32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
         <v>10</v>
       </c>
       <c r="Z32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB32" t="n">
         <v>5</v>
       </c>
-      <c r="AA32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>7</v>
-      </c>
       <c r="AC32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>574469</v>
+        <v>8033165</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -25261,7 +24673,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tracy Aldridge-Jones (HERCULES)</t>
+          <t>Antonia  [HERC]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -25270,100 +24682,82 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="G33" t="n">
         <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>28.595</v>
+        <v>27.002</v>
       </c>
       <c r="I33" t="n">
-        <v>16.168</v>
+        <v>16.817</v>
       </c>
       <c r="J33" t="n">
-        <v>28.495</v>
+        <v>30.24</v>
       </c>
       <c r="K33" t="n">
-        <v>40.755</v>
+        <v>39.277</v>
       </c>
       <c r="L33" t="n">
-        <v>34.098</v>
+        <v>34.838</v>
       </c>
       <c r="M33" t="n">
-        <v>32.928</v>
+        <v>38.838</v>
       </c>
       <c r="N33" t="n">
-        <v>35.976</v>
+        <v>37.318</v>
       </c>
       <c r="O33" t="n">
-        <v>26.636</v>
+        <v>28.878</v>
       </c>
       <c r="P33" t="n">
-        <v>28.14</v>
+        <v>27.918</v>
       </c>
       <c r="Q33" t="n">
-        <v>38.964</v>
+        <v>33.678</v>
       </c>
       <c r="R33" t="n">
-        <v>31.955</v>
+        <v>37.519</v>
       </c>
       <c r="S33" t="n">
-        <v>12.005</v>
+        <v>12</v>
       </c>
       <c r="T33" t="n">
-        <v>28.481</v>
+        <v>6</v>
       </c>
       <c r="U33" t="n">
-        <v>31.07</v>
+        <v>5</v>
       </c>
       <c r="V33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
         <v>7</v>
       </c>
       <c r="X33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA33" t="n">
         <v>9</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC33" t="n">
         <v>5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5609162</v>
+        <v>2692261</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -25377,109 +24771,91 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="G34" t="n">
         <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>25.057</v>
+        <v>28.435</v>
       </c>
       <c r="I34" t="n">
-        <v>16.968</v>
+        <v>17.312</v>
       </c>
       <c r="J34" t="n">
-        <v>29.836</v>
+        <v>30.575</v>
       </c>
       <c r="K34" t="n">
-        <v>40.031</v>
+        <v>44.238</v>
       </c>
       <c r="L34" t="n">
-        <v>44.944</v>
+        <v>36.226</v>
       </c>
       <c r="M34" t="n">
-        <v>42.049</v>
+        <v>36.023</v>
       </c>
       <c r="N34" t="n">
-        <v>39.622</v>
+        <v>39.547</v>
       </c>
       <c r="O34" t="n">
-        <v>31.215</v>
+        <v>24.804</v>
       </c>
       <c r="P34" t="n">
-        <v>36.211</v>
+        <v>30.705</v>
       </c>
       <c r="Q34" t="n">
-        <v>40.636</v>
+        <v>31.805</v>
       </c>
       <c r="R34" t="n">
-        <v>39.792</v>
+        <v>34.64</v>
       </c>
       <c r="S34" t="n">
-        <v>11.321</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>25.944</v>
+        <v>4</v>
       </c>
       <c r="U34" t="n">
-        <v>28.373</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="W34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34" t="n">
         <v>7</v>
       </c>
       <c r="Y34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC34" t="n">
         <v>7</v>
       </c>
-      <c r="Z34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2692261</v>
+        <v>6547311</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -25488,12 +24864,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -25502,100 +24878,82 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>28.435</v>
+        <v>29.149</v>
       </c>
       <c r="I35" t="n">
-        <v>17.312</v>
+        <v>15.962</v>
       </c>
       <c r="J35" t="n">
-        <v>30.575</v>
+        <v>29.941</v>
       </c>
       <c r="K35" t="n">
-        <v>44.238</v>
+        <v>43.701</v>
       </c>
       <c r="L35" t="n">
-        <v>36.226</v>
+        <v>51.88</v>
       </c>
       <c r="M35" t="n">
-        <v>36.023</v>
+        <v>34.65</v>
       </c>
       <c r="N35" t="n">
-        <v>39.547</v>
+        <v>49.818</v>
       </c>
       <c r="O35" t="n">
-        <v>24.804</v>
+        <v>25.599</v>
       </c>
       <c r="P35" t="n">
-        <v>30.705</v>
+        <v>30.419</v>
       </c>
       <c r="Q35" t="n">
-        <v>31.805</v>
+        <v>33.434</v>
       </c>
       <c r="R35" t="n">
-        <v>34.64</v>
+        <v>33</v>
       </c>
       <c r="S35" t="n">
-        <v>11.981</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>27.939</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>30.581</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y35" t="n">
         <v>3</v>
       </c>
       <c r="Z35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA35" t="n">
         <v>6</v>
       </c>
-      <c r="AA35" t="n">
-        <v>7</v>
-      </c>
       <c r="AB35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ35" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6547311</v>
+        <v>5609162</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -25604,110 +24962,92 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="G36" t="n">
         <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>29.149</v>
+        <v>25.057</v>
       </c>
       <c r="I36" t="n">
-        <v>15.962</v>
+        <v>16.968</v>
       </c>
       <c r="J36" t="n">
-        <v>29.941</v>
+        <v>29.836</v>
       </c>
       <c r="K36" t="n">
-        <v>43.701</v>
+        <v>40.031</v>
       </c>
       <c r="L36" t="n">
-        <v>51.88</v>
+        <v>44.944</v>
       </c>
       <c r="M36" t="n">
-        <v>34.65</v>
+        <v>42.049</v>
       </c>
       <c r="N36" t="n">
-        <v>49.818</v>
+        <v>39.622</v>
       </c>
       <c r="O36" t="n">
-        <v>25.599</v>
+        <v>31.215</v>
       </c>
       <c r="P36" t="n">
-        <v>30.419</v>
+        <v>36.211</v>
       </c>
       <c r="Q36" t="n">
-        <v>33.434</v>
+        <v>40.636</v>
       </c>
       <c r="R36" t="n">
-        <v>33</v>
+        <v>39.792</v>
       </c>
       <c r="S36" t="n">
-        <v>11.783</v>
+        <v>18</v>
       </c>
       <c r="T36" t="n">
-        <v>26.566</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
-        <v>29.783</v>
+        <v>7</v>
       </c>
       <c r="V36" t="n">
+        <v>7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA36" t="n">
         <v>3</v>
-      </c>
-      <c r="W36" t="n">
-        <v>8</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>8</v>
       </c>
       <c r="AB36" t="n">
         <v>3</v>
       </c>
       <c r="AC36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ36" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -25734,7 +25074,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G37" t="n">
         <v>3</v>
@@ -25773,57 +25113,39 @@
         <v>39.104</v>
       </c>
       <c r="S37" t="n">
-        <v>12.253</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>29.143</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>32.082</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z37" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB37" t="n">
         <v>4</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD37" t="n">
         <v>4</v>
       </c>
-      <c r="AE37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -25850,7 +25172,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -25889,57 +25211,39 @@
         <v>35.588</v>
       </c>
       <c r="S38" t="n">
-        <v>11.662</v>
+        <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>28.605</v>
+        <v>14</v>
       </c>
       <c r="U38" t="n">
-        <v>25.732</v>
+        <v>12</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="W38" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Y38" t="n">
         <v>20</v>
       </c>
       <c r="Z38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AB38" t="n">
         <v>20</v>
       </c>
       <c r="AC38" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD38" t="n">
         <v>14</v>
       </c>
-      <c r="AE38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -25966,7 +25270,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>230</v>
+        <v>182</v>
       </c>
       <c r="G39" t="n">
         <v>3</v>
@@ -26005,61 +25309,43 @@
         <v>33.993</v>
       </c>
       <c r="S39" t="n">
-        <v>12.471</v>
+        <v>16</v>
       </c>
       <c r="T39" t="n">
-        <v>30.145</v>
+        <v>16</v>
       </c>
       <c r="U39" t="n">
-        <v>32.979</v>
+        <v>16</v>
       </c>
       <c r="V39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="X39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y39" t="n">
         <v>18</v>
       </c>
       <c r="Z39" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="n">
         <v>14</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>18</v>
       </c>
       <c r="AC39" t="n">
         <v>16</v>
       </c>
-      <c r="AD39" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4653373</v>
+        <v>832585</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -26068,12 +25354,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Paul Wa (HERC I)</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -26082,100 +25368,82 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="G40" t="n">
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>29.756</v>
+        <v>32.218</v>
       </c>
       <c r="I40" t="n">
-        <v>14.76</v>
+        <v>19.955</v>
       </c>
       <c r="J40" t="n">
-        <v>31.024</v>
+        <v>35.411</v>
       </c>
       <c r="K40" t="n">
-        <v>43.885</v>
+        <v>43.83</v>
       </c>
       <c r="L40" t="n">
-        <v>40.453</v>
+        <v>37.628</v>
       </c>
       <c r="M40" t="n">
-        <v>38.221</v>
+        <v>36.704</v>
       </c>
       <c r="N40" t="n">
-        <v>39.253</v>
+        <v>39.354</v>
       </c>
       <c r="O40" t="n">
-        <v>27.092</v>
+        <v>29.378</v>
       </c>
       <c r="P40" t="n">
-        <v>39.487</v>
+        <v>30.244</v>
       </c>
       <c r="Q40" t="n">
-        <v>35.69</v>
+        <v>33.584</v>
       </c>
       <c r="R40" t="n">
-        <v>37.487</v>
+        <v>33.749</v>
       </c>
       <c r="S40" t="n">
-        <v>12.196</v>
+        <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>30.857</v>
+        <v>12</v>
       </c>
       <c r="U40" t="n">
-        <v>34.956</v>
+        <v>14</v>
       </c>
       <c r="V40" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="W40" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="X40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="n">
         <v>14</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AB40" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AC40" t="n">
         <v>20</v>
       </c>
-      <c r="AD40" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>832585</v>
+        <v>2648548</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -26184,12 +25452,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -26198,100 +25466,82 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>214</v>
+        <v>172</v>
       </c>
       <c r="G41" t="n">
         <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>32.218</v>
+        <v>30.397</v>
       </c>
       <c r="I41" t="n">
-        <v>19.955</v>
+        <v>16.531</v>
       </c>
       <c r="J41" t="n">
-        <v>35.411</v>
+        <v>31.263</v>
       </c>
       <c r="K41" t="n">
-        <v>43.83</v>
+        <v>43.896</v>
       </c>
       <c r="L41" t="n">
-        <v>37.628</v>
+        <v>38.23</v>
       </c>
       <c r="M41" t="n">
-        <v>36.704</v>
+        <v>36.764</v>
       </c>
       <c r="N41" t="n">
-        <v>39.354</v>
+        <v>39.496</v>
       </c>
       <c r="O41" t="n">
-        <v>29.378</v>
+        <v>29.387</v>
       </c>
       <c r="P41" t="n">
-        <v>30.244</v>
+        <v>29.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>33.584</v>
+        <v>33.629</v>
       </c>
       <c r="R41" t="n">
-        <v>33.749</v>
+        <v>33.829</v>
       </c>
       <c r="S41" t="n">
-        <v>12.423</v>
+        <v>18</v>
       </c>
       <c r="T41" t="n">
-        <v>30.335</v>
+        <v>18</v>
       </c>
       <c r="U41" t="n">
-        <v>36.035</v>
+        <v>18</v>
       </c>
       <c r="V41" t="n">
+        <v>12</v>
+      </c>
+      <c r="W41" t="n">
         <v>14</v>
       </c>
-      <c r="W41" t="n">
+      <c r="X41" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y41" t="n">
         <v>12</v>
       </c>
-      <c r="X41" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>16</v>
-      </c>
       <c r="Z41" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA41" t="n">
         <v>18</v>
       </c>
       <c r="AB41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE41" t="n">
         <v>18</v>
       </c>
-      <c r="AF41" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2648548</v>
+        <v>4653373</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -26305,7 +25555,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Paul Wa (HERC I)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -26314,70 +25564,70 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
       <c r="G42" t="n">
         <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>30.397</v>
+        <v>29.756</v>
       </c>
       <c r="I42" t="n">
-        <v>16.531</v>
+        <v>14.76</v>
       </c>
       <c r="J42" t="n">
-        <v>31.263</v>
+        <v>31.024</v>
       </c>
       <c r="K42" t="n">
-        <v>43.896</v>
+        <v>43.885</v>
       </c>
       <c r="L42" t="n">
-        <v>38.23</v>
+        <v>40.453</v>
       </c>
       <c r="M42" t="n">
-        <v>36.764</v>
+        <v>38.221</v>
       </c>
       <c r="N42" t="n">
-        <v>39.496</v>
+        <v>39.253</v>
       </c>
       <c r="O42" t="n">
-        <v>29.387</v>
+        <v>27.092</v>
       </c>
       <c r="P42" t="n">
-        <v>29.63</v>
+        <v>39.487</v>
       </c>
       <c r="Q42" t="n">
-        <v>33.629</v>
+        <v>35.69</v>
       </c>
       <c r="R42" t="n">
-        <v>33.829</v>
+        <v>37.487</v>
       </c>
       <c r="S42" t="n">
-        <v>12.299</v>
+        <v>20</v>
       </c>
       <c r="T42" t="n">
-        <v>32.896</v>
+        <v>20</v>
       </c>
       <c r="U42" t="n">
-        <v>35.031</v>
+        <v>20</v>
       </c>
       <c r="V42" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W42" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="X42" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y42" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="n">
         <v>12</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>16</v>
       </c>
       <c r="AB42" t="n">
         <v>12</v>
@@ -26385,25 +25635,7 @@
       <c r="AC42" t="n">
         <v>12</v>
       </c>
-      <c r="AD42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -26430,7 +25662,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="G43" t="n">
         <v>3</v>
@@ -26469,13 +25701,13 @@
         <v>38.982</v>
       </c>
       <c r="S43" t="n">
-        <v>14.319</v>
+        <v>20</v>
       </c>
       <c r="T43" t="n">
-        <v>42.786</v>
+        <v>20</v>
       </c>
       <c r="U43" t="n">
-        <v>53.088</v>
+        <v>20</v>
       </c>
       <c r="V43" t="n">
         <v>20</v>
@@ -26501,25 +25733,7 @@
       <c r="AC43" t="n">
         <v>20</v>
       </c>
-      <c r="AD43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LaRoja/LaRoja.xlsx
+++ b/LaRoja/LaRoja.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I321"/>
+  <dimension ref="A1:I322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5357,7 +5357,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>6555777</v>
+        <v>810333</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5366,27 +5366,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jorge Redondo</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Taeho Kim</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>01:54:28.946</t>
+          <t>01:52:58.385</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -5396,7 +5392,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>212239</v>
+        <v>6555777</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5415,27 +5411,27 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>T.seiryo</t>
+          <t>Jorge Redondo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NICO OZ</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>31:54.130</t>
+          <t>01:54:28.946</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5721932</v>
+        <v>212239</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -5454,13 +5450,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dominic Radomski</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
+          <t>T.seiryo</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NICO OZ</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>32:36.168</t>
+          <t>31:54.130</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>58066</v>
+        <v>5721932</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -5484,22 +5484,18 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Drew Morris (BATH CC)</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Team BUK - LDN</t>
-        </is>
-      </c>
+          <t>Dominic Radomski</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>32:36.228</t>
+          <t>32:36.168</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -5509,7 +5505,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>3138161</v>
+        <v>58066</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -5523,22 +5519,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Gus Pettey</t>
+          <t>Drew Morris (BATH CC)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team BUK - LDN</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>32:36.857</t>
+          <t>32:36.228</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -5548,7 +5544,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3737418</v>
+        <v>3138161</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5562,22 +5558,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Gonda Beltman (ZWB)</t>
+          <t>Gus Pettey</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ZWB Cycling</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>32:38.891</t>
+          <t>32:36.857</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -5587,7 +5583,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2626084</v>
+        <v>3737418</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5606,17 +5602,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Michael Richards (ART)</t>
+          <t>Gonda Beltman (ZWB)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ART</t>
+          <t>ZWB Cycling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>32:42.013</t>
+          <t>32:38.891</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -5626,7 +5622,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1433752</v>
+        <v>2626084</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -5640,22 +5636,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Michael Ramsdale</t>
+          <t>Michael Richards (ART)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Army Cycling</t>
+          <t>ART</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>33:05.672</t>
+          <t>32:42.013</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -5665,7 +5661,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>789197</v>
+        <v>1433752</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -5679,18 +5675,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Barry Stewart</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+          <t>Michael Ramsdale</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Army Cycling</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>33:20.176</t>
+          <t>33:05.672</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>940950</v>
+        <v>789197</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -5719,13 +5719,13 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Max-Hiroyuki</t>
+          <t>Barry Stewart</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>33:40.165</t>
+          <t>33:20.176</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>506152</v>
+        <v>940950</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5749,22 +5749,18 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2707 Buache Philippe [3CY]</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>3 Cycles [3CY]</t>
-        </is>
-      </c>
+          <t>Max-Hiroyuki</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>34:15.156</t>
+          <t>33:40.165</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -5774,7 +5770,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>247483</v>
+        <v>506152</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5788,18 +5784,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>k quinone</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
+          <t>2707 Buache Philippe [3CY]</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>3 Cycles [3CY]</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>34:24.188</t>
+          <t>34:15.156</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6062725</v>
+        <v>247483</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5823,18 +5823,18 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>James Hoffmann</t>
+          <t>k quinone</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>34:26.054</t>
+          <t>34:24.188</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -5844,7 +5844,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2726434</v>
+        <v>6062725</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5858,22 +5858,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Serge Lebeau - FFZ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>FFZ</t>
-        </is>
-      </c>
+          <t>James Hoffmann</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>34:26.267</t>
+          <t>34:26.054</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -5883,7 +5879,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>972431</v>
+        <v>2726434</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5897,22 +5893,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Daniel Brejwo3834</t>
+          <t>Serge Lebeau - FFZ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>FFZ</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>34:53.581</t>
+          <t>34:26.267</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -5922,7 +5918,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>440496</v>
+        <v>972431</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5936,22 +5932,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Magnus  Andersson [SZ]</t>
+          <t>Daniel Brejwo3834</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>35:03.557</t>
+          <t>34:53.581</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -5961,7 +5957,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>354</v>
+        <v>440496</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5970,27 +5966,27 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Anthony Cree [EVO/FSR]</t>
+          <t>Magnus  Andersson [SZ]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>35:11.390</t>
+          <t>35:03.557</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -6000,7 +5996,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>436383</v>
+        <v>354</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -6009,7 +6005,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -6019,17 +6015,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Michael Hailes [RWB Dragons]</t>
+          <t>Anthony Cree [EVO/FSR]</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>35:11.809</t>
+          <t>35:11.390</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -6039,7 +6035,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2926600</v>
+        <v>436383</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -6053,22 +6049,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Charles LaBerge (TFC)</t>
+          <t>Michael Hailes [RWB Dragons]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>35:27.389</t>
+          <t>35:11.809</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -6078,7 +6074,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>5270396</v>
+        <v>2926600</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -6092,22 +6088,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Matthew Hickey [Velos]</t>
+          <t>Charles LaBerge (TFC)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Team Velos</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>35:45.967</t>
+          <t>35:27.389</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -6117,7 +6113,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>6991072</v>
+        <v>5270396</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -6126,27 +6122,27 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Matthew Hickey [Velos]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team Velos</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>35:48.305</t>
+          <t>35:45.967</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -6156,7 +6152,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>3829038</v>
+        <v>6991072</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -6165,27 +6161,27 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Henry Gilroy</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>TeamODZ</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>35:53.056</t>
+          <t>35:48.305</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
@@ -6195,7 +6191,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>6053812</v>
+        <v>3829038</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -6214,13 +6210,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>David Ed</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
+          <t>Henry Gilroy</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>TeamODZ</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>35:53.684</t>
+          <t>35:53.056</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>5763315</v>
+        <v>6053812</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -6239,27 +6239,23 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nick Katagiri (CYE)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>CYE</t>
-        </is>
-      </c>
+          <t>David Ed</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>36:25.342</t>
+          <t>35:53.684</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -6269,7 +6265,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2300022</v>
+        <v>5763315</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -6278,23 +6274,27 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Takashi  Miyajima</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>Nick Katagiri (CYE)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>CYE</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>36:38.215</t>
+          <t>36:25.342</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>5851455</v>
+        <v>2300022</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -6313,27 +6313,23 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>taku hata</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Takashi  Miyajima</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>36:40.478</t>
+          <t>36:38.215</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -6343,7 +6339,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>4756645</v>
+        <v>5851455</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -6352,7 +6348,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6362,17 +6358,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Jordan Sahlie</t>
+          <t>taku hata</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>36:41.546</t>
+          <t>36:40.478</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -6382,7 +6378,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>779638</v>
+        <v>4756645</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -6391,23 +6387,27 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tiana Abel</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>Jordan Sahlie</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>36:44.360</t>
+          <t>36:41.546</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>3094251</v>
+        <v>779638</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6426,23 +6426,23 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Marijn Sax</t>
+          <t>Tiana Abel</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>43:36.853</t>
+          <t>36:44.360</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1555566</v>
+        <v>3094251</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6466,18 +6466,18 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Jo Earrey</t>
+          <t>Marijn Sax</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>44:00.947</t>
+          <t>43:36.853</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -6487,7 +6487,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2858658</v>
+        <v>1555566</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -6506,17 +6506,13 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ryan Ness</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>TFC</t>
-        </is>
-      </c>
+          <t>Jo Earrey</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>44:23.440</t>
+          <t>44:00.947</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -6526,7 +6522,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>630224</v>
+        <v>2858658</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -6540,22 +6536,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Jeffrey Thistle(TNP)</t>
+          <t>Ryan Ness</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>44:32.267</t>
+          <t>44:23.440</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
@@ -6565,7 +6561,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3011420</v>
+        <v>630224</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -6579,22 +6575,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Jonny Okon [CTB]</t>
+          <t>Jeffrey Thistle(TNP)</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CTB</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>44:46.762</t>
+          <t>44:32.267</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
@@ -6604,7 +6600,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>186909</v>
+        <v>3011420</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -6623,17 +6619,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tom Carmeliet</t>
+          <t>Jonny Okon [CTB]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>BZR eCycling Club</t>
+          <t>CTB</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>45:50.414</t>
+          <t>44:46.762</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -6643,7 +6639,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>7513624</v>
+        <v>186909</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -6657,18 +6653,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Casey Morgan</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
+          <t>Tom Carmeliet</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>BZR eCycling Club</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>46:03.528</t>
+          <t>45:50.414</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -6678,7 +6678,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2476913</v>
+        <v>7513624</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -6697,17 +6697,13 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Gary Barham [Team CLS]</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Team CLS</t>
-        </is>
-      </c>
+          <t>Casey Morgan</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>47:09.347</t>
+          <t>46:03.528</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
@@ -6717,7 +6713,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>5141401</v>
+        <v>2476913</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -6726,27 +6722,27 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>James L-J</t>
+          <t>Gary Barham [Team CLS]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>47:10.955</t>
+          <t>47:09.347</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
@@ -6756,7 +6752,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2291008</v>
+        <v>5141401</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -6770,22 +6766,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrew Heppell (CRYO-GEN GROSSGLOCKNER) </t>
+          <t>James L-J</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>47:54.124</t>
+          <t>47:10.955</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -6795,7 +6791,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4273591</v>
+        <v>2291008</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -6804,27 +6800,27 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Karol Borowiak [BH-eRT]</t>
+          <t xml:space="preserve">Andrew Heppell (CRYO-GEN GROSSGLOCKNER) </t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>BH-eRT</t>
+          <t>Team CRYO-GEN</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>49:59.929</t>
+          <t>47:54.124</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
@@ -6834,7 +6830,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>415815</v>
+        <v>4273591</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -6843,27 +6839,27 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ole Koch</t>
+          <t>Karol Borowiak [BH-eRT]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TMA</t>
+          <t>BH-eRT</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>57:38.248</t>
+          <t>49:59.929</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
@@ -6873,7 +6869,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1728056</v>
+        <v>415815</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -6887,22 +6883,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Tom Robson [ART]</t>
+          <t>Ole Koch</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ART</t>
+          <t>TMA</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>58:33.504</t>
+          <t>57:38.248</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -6912,7 +6908,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>432617</v>
+        <v>1728056</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -6931,17 +6927,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Martin Glavind [PCH]</t>
+          <t>Tom Robson [ART]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PainCavesHeroes</t>
+          <t>ART</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>58:33.965</t>
+          <t>58:33.504</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
@@ -6951,7 +6947,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>5268990</v>
+        <v>432617</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6965,18 +6961,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Niels Lambertsen(GoNuts)</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
+          <t>Martin Glavind [PCH]</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>PainCavesHeroes</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>58:35.774</t>
+          <t>58:33.965</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1659675</v>
+        <v>5268990</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -7000,22 +7000,18 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Paul Pierson (EGCC)</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>EGCC - UK</t>
-        </is>
-      </c>
+          <t>Niels Lambertsen(GoNuts)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>59:25.519</t>
+          <t>58:35.774</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -7025,7 +7021,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>693148</v>
+        <v>1659675</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -7039,22 +7035,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Darrel Handley(Level)</t>
+          <t>Paul Pierson (EGCC)</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>EGCC - UK</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>01:00:23.876</t>
+          <t>59:25.519</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -7064,7 +7060,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1962385</v>
+        <v>693148</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -7078,22 +7074,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Jonny Newcombe [SRT]</t>
+          <t>Darrel Handley(Level)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>01:00:50.102</t>
+          <t>01:00:23.876</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -7103,7 +7099,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>8389259</v>
+        <v>1962385</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -7117,18 +7113,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Morten  Damgaard Andersen [eCKD]</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+          <t>Jonny Newcombe [SRT]</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>S R T</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>01:01:05.959</t>
+          <t>01:00:50.102</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2458483</v>
+        <v>8389259</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -7147,23 +7147,23 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Takashi Kanno&amp;#65288;&amp;#37444;&amp;#36554;&amp;#36650;&amp;#65289;</t>
+          <t>Morten  Damgaard Andersen [eCKD]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>01:01:06.870</t>
+          <t>01:01:05.959</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>7349351</v>
+        <v>2458483</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -7182,27 +7182,23 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Fin Stephen (TNP)</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Takashi Kanno&amp;#65288;&amp;#37444;&amp;#36554;&amp;#36650;&amp;#65289;</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>01:01:14.126</t>
+          <t>01:01:06.870</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -7212,7 +7208,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>3477462</v>
+        <v>7349351</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -7221,27 +7217,27 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Jay ONeil</t>
+          <t>Fin Stephen (TNP)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>01:01:46.913</t>
+          <t>01:01:14.126</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -7251,7 +7247,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>646921</v>
+        <v>3477462</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -7265,18 +7261,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kamil Jablonski</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
+          <t>Jay ONeil</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>01:03:08.128</t>
+          <t>01:01:46.913</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4755128</v>
+        <v>646921</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -7305,17 +7305,13 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Chuck Worn</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>SISU Racing</t>
-        </is>
-      </c>
+          <t>Kamil Jablonski</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>01:03:23.946</t>
+          <t>01:03:08.128</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
@@ -7325,7 +7321,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>5219378</v>
+        <v>4755128</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -7339,22 +7335,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Bernard Huijbers</t>
+          <t>Chuck Worn</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ride15</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>01:03:24.064</t>
+          <t>01:03:23.946</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
@@ -7364,7 +7360,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>4451629</v>
+        <v>5219378</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -7378,22 +7374,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Edwin Otto Team NL B3</t>
+          <t>Bernard Huijbers</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TeamNL</t>
+          <t>Ride15</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>01:03:25.350</t>
+          <t>01:03:24.064</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
@@ -7403,7 +7399,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>3261848</v>
+        <v>4451629</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -7417,22 +7413,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Toby Pendlebury</t>
+          <t>Edwin Otto Team NL B3</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>G8TR</t>
+          <t>TeamNL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>01:03:26.476</t>
+          <t>01:03:25.350</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
@@ -7442,7 +7438,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>5369327</v>
+        <v>3261848</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -7456,22 +7452,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dave Wilkinson  </t>
+          <t>Toby Pendlebury</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>KendalCCRacing</t>
+          <t>G8TR</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>01:03:40.830</t>
+          <t>01:03:26.476</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
@@ -7481,7 +7477,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>810333</v>
+        <v>5369327</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -7490,23 +7486,27 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Taeho Kim</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
+          <t xml:space="preserve">Dave Wilkinson  </t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>KendalCCRacing</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>01:04:17.535</t>
+          <t>01:03:40.830</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
@@ -9688,7 +9688,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>3246105</v>
+        <v>6249090</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -9697,23 +9697,27 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>David Priest</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr"/>
+          <t>Juan Jose Fondevila</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>BETENDURANCE</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>49:07.073</t>
+          <t>48:46.994</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -9723,7 +9727,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1607981</v>
+        <v>3246105</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -9737,22 +9741,18 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>John Foley</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Cycling Ireland</t>
-        </is>
-      </c>
+          <t>David Priest</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>49:39.779</t>
+          <t>49:07.073</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
@@ -9762,7 +9762,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>5818155</v>
+        <v>1607981</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -9776,22 +9776,22 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Christopher Schwartke</t>
+          <t>John Foley</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>Cycling Ireland</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>50:08.622</t>
+          <t>49:39.779</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>5922603</v>
+        <v>5818155</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -9820,13 +9820,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Dmitry Stankevich [MTBtraining]</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr"/>
+          <t>Christopher Schwartke</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>50:26.645</t>
+          <t>50:08.622</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
@@ -9836,7 +9840,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>3791286</v>
+        <v>5922603</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -9850,22 +9854,18 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrew  Black TNP </t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Dmitry Stankevich [MTBtraining]</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>50:37.515</t>
+          <t>50:26.645</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
@@ -9875,7 +9875,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1343767</v>
+        <v>3791286</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -9889,18 +9889,22 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mikkel  Andkjaer </t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr"/>
+          <t xml:space="preserve">Andrew  Black TNP </t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>01:00:22.458</t>
+          <t>50:37.515</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
@@ -9910,7 +9914,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>6978253</v>
+        <v>1343767</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -9924,18 +9928,18 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>V incent</t>
+          <t xml:space="preserve">Mikkel  Andkjaer </t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>01:01:39.547</t>
+          <t>01:00:22.458</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
@@ -9945,7 +9949,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>4941002</v>
+        <v>6978253</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -9959,22 +9963,18 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Dai Wai</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>teamWKG</t>
-        </is>
-      </c>
+          <t>V incent</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>01:04:14.441</t>
+          <t>01:01:39.547</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -9984,7 +9984,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1403013</v>
+        <v>4941002</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -9998,22 +9998,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sven F&amp;ouml;rster5715</t>
+          <t>Dai Wai</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Talent:frei p/b Baldiso</t>
+          <t>teamWKG</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>01:04:18.458</t>
+          <t>01:04:14.441</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -10023,7 +10023,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>611137</v>
+        <v>1403013</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -10032,23 +10032,27 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">D. M&amp;uuml;ller </t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
+          <t>Sven F&amp;ouml;rster5715</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Talent:frei p/b Baldiso</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>01:04:26.259</t>
+          <t>01:04:18.458</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -10058,7 +10062,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>98867</v>
+        <v>611137</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -10067,23 +10071,23 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>gavin potter</t>
+          <t xml:space="preserve">D. M&amp;uuml;ller </t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>01:05:02.593</t>
+          <t>01:04:26.259</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
@@ -10093,7 +10097,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>727528</v>
+        <v>98867</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -10102,27 +10106,23 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Steve Pollard WBR 2547</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>gavin potter</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>01:06:22.591</t>
+          <t>01:05:02.593</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1310445</v>
+        <v>727528</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -10146,18 +10146,22 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>S&amp;oslash;ren Pedersen #BBB#</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
+          <t>Steve Pollard WBR 2547</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>01:06:30.425</t>
+          <t>01:06:22.591</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
@@ -10167,7 +10171,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>4870988</v>
+        <v>1310445</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -10176,27 +10180,23 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>.Mauro (TSE)</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>TSE</t>
-        </is>
-      </c>
+          <t>S&amp;oslash;ren Pedersen #BBB#</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>01:07:19.715</t>
+          <t>01:06:30.425</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>829753</v>
+        <v>4870988</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -10220,22 +10220,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Mat Man. [VCRT]</t>
+          <t>.Mauro (TSE)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>VCRT</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>01:07:20.310</t>
+          <t>01:07:19.715</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
@@ -10245,7 +10245,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>5507196</v>
+        <v>829753</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -10259,22 +10259,22 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Jeroen Wigard</t>
+          <t>Mat Man. [VCRT]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>VCRT</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>01:07:22.666</t>
+          <t>01:07:20.310</t>
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
@@ -10284,7 +10284,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>601614</v>
+        <v>5507196</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -10303,17 +10303,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sven Koch</t>
+          <t>Jeroen Wigard</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>TMA</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>01:07:22.943</t>
+          <t>01:07:22.666</t>
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
@@ -10323,7 +10323,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>875004</v>
+        <v>601614</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -10342,13 +10342,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Zain Upton</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
+          <t>Sven Koch</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>TMA</t>
+        </is>
+      </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>01:08:13.117</t>
+          <t>01:07:22.943</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
@@ -10358,7 +10362,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>4132421</v>
+        <v>875004</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -10372,18 +10376,18 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>a yamamoto</t>
+          <t>Zain Upton</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>01:10:05.248</t>
+          <t>01:08:13.117</t>
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
@@ -10393,7 +10397,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>284739</v>
+        <v>4132421</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -10407,22 +10411,18 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mike Alford [EVO]</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>a yamamoto</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>01:10:27.844</t>
+          <t>01:10:05.248</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
@@ -10432,7 +10432,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1085903</v>
+        <v>284739</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -10446,18 +10446,22 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Chris B.</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
+          <t>Mike Alford [EVO]</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>01:11:02.240</t>
+          <t>01:10:27.844</t>
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
@@ -10467,7 +10471,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>279941</v>
+        <v>1085903</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -10476,27 +10480,23 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Gert Gerges</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>DBR</t>
-        </is>
-      </c>
+          <t>Chris B.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>01:12:11.580</t>
+          <t>01:11:02.240</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
@@ -10506,18 +10506,18 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>7853050</v>
+        <v>279941</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="D262" t="inlineStr">
         <is>
           <t>50+</t>
@@ -10525,31 +10525,27 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>&amp;#9854; Talyn [HERC] &amp;#127487;&amp;#127462;</t>
+          <t>Gert Gerges</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>02:37:32.325</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:12:11.580</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
       <c r="I262" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>832585</v>
+        <v>7853050</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -10563,12 +10559,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>&amp;#9854; Talyn [HERC] &amp;#127487;&amp;#127462;</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -10578,12 +10574,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>02:37:40.252</t>
+          <t>02:37:32.325</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>07.927</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="I263" t="n">
@@ -10592,7 +10588,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>2648548</v>
+        <v>832585</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -10601,17 +10597,17 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -10621,12 +10617,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>02:40:18.329</t>
+          <t>02:37:40.252</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>02:46.004</t>
+          <t>07.927</t>
         </is>
       </c>
       <c r="I264" t="n">
@@ -10635,7 +10631,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>4653373</v>
+        <v>2648548</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -10649,12 +10645,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Paul Wa (HERC I)</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -10664,12 +10660,12 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>02:41:00.488</t>
+          <t>02:40:18.329</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>03:28.163</t>
+          <t>02:46.004</t>
         </is>
       </c>
       <c r="I265" t="n">
@@ -10678,7 +10674,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>7529924</v>
+        <v>4653373</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -10692,12 +10688,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Peter Whitelegg&amp;#129385;[HERC]</t>
+          <t>Paul Wa (HERC I)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -10707,12 +10703,12 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>02:54:24.204</t>
+          <t>02:41:00.488</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>16:51.879</t>
+          <t>03:28.163</t>
         </is>
       </c>
       <c r="I266" t="n">
@@ -10721,7 +10717,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>3789457</v>
+        <v>7529924</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -10730,33 +10726,41 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Stuart Williams (TNP)</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr"/>
+          <t>Peter Whitelegg&amp;#129385;[HERC]</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>01:26:22.535</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr"/>
+          <t>02:54:24.204</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>16:51.879</t>
+        </is>
+      </c>
       <c r="I267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>3089483</v>
+        <v>3789457</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -10770,22 +10774,18 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Jonathan Hindle</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Stuart Williams (TNP)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>01:29:03.700</t>
+          <t>01:26:22.535</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
@@ -10795,7 +10795,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>3825702</v>
+        <v>3089483</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Andrew Platts (Rhino)</t>
+          <t>Jonathan Hindle</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>01:45:46.622</t>
+          <t>01:29:03.700</t>
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>5092669</v>
+        <v>3825702</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -10843,27 +10843,27 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Brendan Green</t>
+          <t>Andrew Platts (Rhino)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Team AHDR</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>01:47:27.893</t>
+          <t>01:45:46.622</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
@@ -10873,7 +10873,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1645721</v>
+        <v>5092669</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -10887,18 +10887,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>80+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Raymond SIMON 1613</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr"/>
+          <t>Brendan Green</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Team AHDR</t>
+        </is>
+      </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>01:49:15.958</t>
+          <t>01:47:27.893</t>
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
@@ -10908,7 +10912,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1260805</v>
+        <v>1645721</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -10917,33 +10921,33 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>80+</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Kris Hillmann</t>
+          <t>Raymond SIMON 1613</t>
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>36:55.130</t>
+          <t>01:49:15.958</t>
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>3867579</v>
+        <v>1260805</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -10957,18 +10961,18 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Thomas Tjellstr&amp;ouml;m</t>
+          <t>Kris Hillmann</t>
         </is>
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>36:56.090</t>
+          <t>36:55.130</t>
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
@@ -10978,7 +10982,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>6444865</v>
+        <v>3867579</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -10997,17 +11001,13 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Ian Grant</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Thomas Tjellstr&amp;ouml;m</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>36:57.135</t>
+          <t>36:56.090</t>
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
@@ -11017,7 +11017,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>7971072</v>
+        <v>6444865</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -11031,18 +11031,22 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Alix Gilsoul</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr"/>
+          <t>Ian Grant</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>37:01.354</t>
+          <t>36:57.135</t>
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
@@ -11052,7 +11056,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>5947439</v>
+        <v>7971072</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -11066,18 +11070,18 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>David Gilabert</t>
+          <t>Alix Gilsoul</t>
         </is>
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>37:03.265</t>
+          <t>37:01.354</t>
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
@@ -11087,7 +11091,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>808487</v>
+        <v>5947439</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -11101,22 +11105,18 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Chris Juliano</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>BikeSurgeon</t>
-        </is>
-      </c>
+          <t>David Gilabert</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>37:03.336</t>
+          <t>37:03.265</t>
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1805615</v>
+        <v>808487</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -11145,13 +11145,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Hector   Bustos</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr"/>
+          <t>Chris Juliano</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>BikeSurgeon</t>
+        </is>
+      </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>37:34.172</t>
+          <t>37:03.336</t>
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
@@ -11161,7 +11165,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>61261</v>
+        <v>1805615</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -11170,27 +11174,23 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ingo Sch&amp;ouml;rgenhummer [R2]</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>RuhrRiders</t>
-        </is>
-      </c>
+          <t>Hector   Bustos</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
-          <t>39:12.661</t>
+          <t>37:34.172</t>
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
@@ -11200,7 +11200,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>328851</v>
+        <v>61261</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -11209,27 +11209,27 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Ian Anderson</t>
+          <t>Ingo Sch&amp;ouml;rgenhummer [R2]</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>ZCC</t>
+          <t>RuhrRiders</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>39:17.540</t>
+          <t>39:12.661</t>
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
@@ -11239,7 +11239,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>5491339</v>
+        <v>328851</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -11248,27 +11248,27 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Brian Benner (HERC)</t>
+          <t>Ian Anderson</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>ZCC</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>39:37.997</t>
+          <t>39:17.540</t>
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
@@ -11278,7 +11278,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>2348460</v>
+        <v>5491339</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -11287,23 +11287,27 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>L Stopp</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr"/>
+          <t>Brian Benner (HERC)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>39:42.456</t>
+          <t>39:37.997</t>
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
@@ -11313,7 +11317,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>4986457</v>
+        <v>2348460</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -11327,22 +11331,18 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Jc Vera [PTA2]</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>PTA2</t>
-        </is>
-      </c>
+          <t>L Stopp</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>39:50.644</t>
+          <t>39:42.456</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
@@ -11352,7 +11352,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>532857</v>
+        <v>4986457</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -11366,22 +11366,22 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Gareth Walsh (TFC THOR)</t>
+          <t>Jc Vera [PTA2]</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>PTA2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>40:27.829</t>
+          <t>39:50.644</t>
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>3676652</v>
+        <v>532857</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -11405,22 +11405,22 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>James Gosney4261 (Snow)</t>
+          <t>Gareth Walsh (TFC THOR)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>41:03.642</t>
+          <t>40:27.829</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
@@ -11430,7 +11430,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>8485373</v>
+        <v>3676652</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -11444,18 +11444,22 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Kyle Jones</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr"/>
+          <t>James Gosney4261 (Snow)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>SNOW</t>
+        </is>
+      </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>41:06.615</t>
+          <t>41:03.642</t>
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
@@ -11465,7 +11469,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1272972</v>
+        <v>8485373</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -11474,27 +11478,23 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Heather Clontarf CC </t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>CCC</t>
-        </is>
-      </c>
+          <t>Kyle Jones</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
-          <t>41:07.935</t>
+          <t>41:06.615</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>7477688</v>
+        <v>1272972</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -11523,17 +11523,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>James O&amp;#039;Hare</t>
+          <t xml:space="preserve">Mark Heather Clontarf CC </t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>NewkyBroon</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>41:22.571</t>
+          <t>41:07.935</t>
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
@@ -11543,7 +11543,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>2862621</v>
+        <v>7477688</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -11562,13 +11562,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>- Rippers</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr"/>
+          <t>James O&amp;#039;Hare</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>NewkyBroon</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>41:38.715</t>
+          <t>41:22.571</t>
         </is>
       </c>
       <c r="H289" t="inlineStr"/>
@@ -11578,7 +11582,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1134947</v>
+        <v>2862621</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -11587,7 +11591,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -11597,17 +11601,13 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>red Racer</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ATP </t>
-        </is>
-      </c>
+          <t>- Rippers</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
-          <t>42:06.313</t>
+          <t>41:38.715</t>
         </is>
       </c>
       <c r="H290" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>8515354</v>
+        <v>1134947</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -11631,22 +11631,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>elliot roosens</t>
+          <t>red Racer</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>BIKES &amp;#11088;&amp;#65039;</t>
+          <t xml:space="preserve">ATP </t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>42:13.731</t>
+          <t>42:06.313</t>
         </is>
       </c>
       <c r="H291" t="inlineStr"/>
@@ -11656,7 +11656,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>3520069</v>
+        <v>8515354</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -11665,23 +11665,27 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>James Dawson</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr"/>
+          <t>elliot roosens</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>42:28.676</t>
+          <t>42:13.731</t>
         </is>
       </c>
       <c r="H292" t="inlineStr"/>
@@ -11691,7 +11695,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>7357862</v>
+        <v>3520069</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -11700,23 +11704,23 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Mr Long</t>
+          <t>James Dawson</t>
         </is>
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>42:55.866</t>
+          <t>42:28.676</t>
         </is>
       </c>
       <c r="H293" t="inlineStr"/>
@@ -11726,7 +11730,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>3463649</v>
+        <v>7357862</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -11740,18 +11744,18 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Werner Menzinger</t>
+          <t>Mr Long</t>
         </is>
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>43:38.464</t>
+          <t>42:55.866</t>
         </is>
       </c>
       <c r="H294" t="inlineStr"/>
@@ -11761,7 +11765,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1381745</v>
+        <v>3463649</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -11770,7 +11774,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -11780,13 +11784,13 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Martin Dale</t>
+          <t>Werner Menzinger</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>45:32.253</t>
+          <t>43:38.464</t>
         </is>
       </c>
       <c r="H295" t="inlineStr"/>
@@ -11796,7 +11800,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1417309</v>
+        <v>1381745</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -11805,23 +11809,23 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>70+</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>C hris</t>
+          <t>Martin Dale</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
-          <t>46:22.808</t>
+          <t>45:32.253</t>
         </is>
       </c>
       <c r="H296" t="inlineStr"/>
@@ -11831,7 +11835,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>4862807</v>
+        <v>1417309</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -11850,13 +11854,13 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Hayden White</t>
+          <t>C hris</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
-          <t>46:29.734</t>
+          <t>46:22.808</t>
         </is>
       </c>
       <c r="H297" t="inlineStr"/>
@@ -11866,7 +11870,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>120891</v>
+        <v>4862807</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -11875,23 +11879,23 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Takeru Takehisa</t>
+          <t>Hayden White</t>
         </is>
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>46:55.470</t>
+          <t>46:29.734</t>
         </is>
       </c>
       <c r="H298" t="inlineStr"/>
@@ -11901,7 +11905,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>3568483</v>
+        <v>120891</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -11915,22 +11919,18 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>John O  (HERC/EZR)</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Takeru Takehisa</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
-          <t>48:49.790</t>
+          <t>46:55.470</t>
         </is>
       </c>
       <c r="H299" t="inlineStr"/>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>4329060</v>
+        <v>3568483</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -11959,13 +11959,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Stu Chirnside</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr"/>
+          <t>John O  (HERC/EZR)</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>51:35.298</t>
+          <t>48:49.790</t>
         </is>
       </c>
       <c r="H300" t="inlineStr"/>
@@ -11975,7 +11979,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1576625</v>
+        <v>4329060</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -11984,23 +11988,23 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Data Vader</t>
+          <t>Stu Chirnside</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>51:47.878</t>
+          <t>51:35.298</t>
         </is>
       </c>
       <c r="H301" t="inlineStr"/>
@@ -12010,7 +12014,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>402420</v>
+        <v>1576625</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -12029,17 +12033,13 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Ivan Ischia [ITAFT]</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Team Italy</t>
-        </is>
-      </c>
+          <t>Data Vader</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>52:37.876</t>
+          <t>51:47.878</t>
         </is>
       </c>
       <c r="H302" t="inlineStr"/>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>2332799</v>
+        <v>402420</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -12058,17 +12058,17 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Andrea  D@W</t>
+          <t>Ivan Ischia [ITAFT]</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>52:59.664</t>
+          <t>52:37.876</t>
         </is>
       </c>
       <c r="H303" t="inlineStr"/>
@@ -12088,7 +12088,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1496021</v>
+        <v>2332799</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -12097,27 +12097,27 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Ralf Breuer [Eintracht]</t>
+          <t>Andrea  D@W</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Eintracht Radsport &amp;#129413;</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>53:11.906</t>
+          <t>52:59.664</t>
         </is>
       </c>
       <c r="H304" t="inlineStr"/>
@@ -12127,7 +12127,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>7606805</v>
+        <v>1496021</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -12141,22 +12141,22 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Anya Bukharina [MTBtraining]</t>
+          <t>Ralf Breuer [Eintracht]</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>Eintracht Radsport &amp;#129413;</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>53:14.484</t>
+          <t>53:11.906</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -12166,7 +12166,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>2712565</v>
+        <v>7606805</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -12175,23 +12175,27 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Barry Rose</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
+          <t>Anya Bukharina [MTBtraining]</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>MTBtraining</t>
+        </is>
+      </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>55:02.720</t>
+          <t>53:14.484</t>
         </is>
       </c>
       <c r="H306" t="inlineStr"/>
@@ -12201,7 +12205,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>5639610</v>
+        <v>2712565</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -12215,18 +12219,18 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>K ris Res</t>
+          <t>Barry Rose</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="inlineStr">
         <is>
-          <t>56:58.098</t>
+          <t>55:02.720</t>
         </is>
       </c>
       <c r="H307" t="inlineStr"/>
@@ -12236,7 +12240,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1027344</v>
+        <v>5639610</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -12250,18 +12254,18 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Teresa    Webb TN Multisports</t>
+          <t>K ris Res</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>01:02:04.091</t>
+          <t>56:58.098</t>
         </is>
       </c>
       <c r="H308" t="inlineStr"/>
@@ -12271,7 +12275,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>2617763</v>
+        <v>1027344</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -12280,23 +12284,23 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Will Brennan</t>
+          <t>Teresa    Webb TN Multisports</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="inlineStr">
         <is>
-          <t>01:10:05.198</t>
+          <t>01:02:04.091</t>
         </is>
       </c>
       <c r="H309" t="inlineStr"/>
@@ -12306,7 +12310,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>7143532</v>
+        <v>2617763</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -12315,23 +12319,23 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Ian Howsare</t>
+          <t>Will Brennan</t>
         </is>
       </c>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
-          <t>01:12:06.900</t>
+          <t>01:10:05.198</t>
         </is>
       </c>
       <c r="H310" t="inlineStr"/>
@@ -12341,7 +12345,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>874418</v>
+        <v>7143532</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -12355,18 +12359,18 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Owen Koslow (buckaroos)</t>
+          <t>Ian Howsare</t>
         </is>
       </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="inlineStr">
         <is>
-          <t>01:12:28.559</t>
+          <t>01:12:06.900</t>
         </is>
       </c>
       <c r="H311" t="inlineStr"/>
@@ -12376,7 +12380,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>3693758</v>
+        <v>874418</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -12390,18 +12394,18 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Przemek Bagi&amp;#324;ski</t>
+          <t>Owen Koslow (buckaroos)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
-          <t>01:12:40.398</t>
+          <t>01:12:28.559</t>
         </is>
       </c>
       <c r="H312" t="inlineStr"/>
@@ -12411,7 +12415,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>83940</v>
+        <v>3693758</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -12420,27 +12424,23 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Ledcrow Yi</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>CaM</t>
-        </is>
-      </c>
+          <t>Przemek Bagi&amp;#324;ski</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
-          <t>01:13:17.611</t>
+          <t>01:12:40.398</t>
         </is>
       </c>
       <c r="H313" t="inlineStr"/>
@@ -12450,7 +12450,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>146839</v>
+        <v>83940</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -12469,13 +12469,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Tony Hirst</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr"/>
+          <t>Ledcrow Yi</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>CaM</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>01:15:15.479</t>
+          <t>01:13:17.611</t>
         </is>
       </c>
       <c r="H314" t="inlineStr"/>
@@ -12485,7 +12489,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>6942033</v>
+        <v>146839</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -12494,23 +12498,23 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Jan Jantzen</t>
+          <t>Tony Hirst</t>
         </is>
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr">
         <is>
-          <t>01:17:25.335</t>
+          <t>01:15:15.479</t>
         </is>
       </c>
       <c r="H315" t="inlineStr"/>
@@ -12520,7 +12524,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>6386594</v>
+        <v>6942033</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -12529,23 +12533,23 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Gibo Di Longi (AGTB) (GTR)</t>
+          <t>Jan Jantzen</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="inlineStr">
         <is>
-          <t>01:18:47.645</t>
+          <t>01:17:25.335</t>
         </is>
       </c>
       <c r="H316" t="inlineStr"/>
@@ -12555,16 +12559,16 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>3837944</v>
+        <v>6386594</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -12574,31 +12578,23 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>GTR</t>
-        </is>
-      </c>
+          <t>Gibo Di Longi (AGTB) (GTR)</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="inlineStr">
         <is>
-          <t>05:40:35.461</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
+          <t>01:18:47.645</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
       <c r="I317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>8490710</v>
+        <v>3837944</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -12607,33 +12603,41 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Edi Edi</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr"/>
+          <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>41:04.269</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr"/>
+          <t>05:40:35.461</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
       <c r="I318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>127818</v>
+        <v>8490710</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -12642,27 +12646,23 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Nick Ske</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>TriLakes</t>
-        </is>
-      </c>
+          <t>Edi Edi</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
       <c r="G319" t="inlineStr">
         <is>
-          <t>51:11.419</t>
+          <t>41:04.269</t>
         </is>
       </c>
       <c r="H319" t="inlineStr"/>
@@ -12672,7 +12672,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>6069479</v>
+        <v>127818</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -12686,18 +12686,22 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Andreas Kintzel</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr"/>
+          <t>Nick Ske</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>TriLakes</t>
+        </is>
+      </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>01:22:59.360</t>
+          <t>51:11.419</t>
         </is>
       </c>
       <c r="H320" t="inlineStr"/>
@@ -12707,7 +12711,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1227468</v>
+        <v>6069479</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -12721,22 +12725,57 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>scott lambert</t>
+          <t>Andreas Kintzel</t>
         </is>
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="inlineStr">
         <is>
-          <t>01:25:18.065</t>
+          <t>01:22:59.360</t>
         </is>
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>1227468</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Mas</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>scott lambert</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>01:25:18.065</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14492,7 +14531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19950,12 +19989,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cycling Ireland</t>
+          <t>BETENDURANCE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>49:39.779</t>
+          <t>48:46.994</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -19984,7 +20023,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>49:39.779</t>
+          <t>48:46.994</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -19999,12 +20038,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>Cycling Ireland</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>50:08.622</t>
+          <t>49:39.779</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -20033,7 +20072,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>50:08.622</t>
+          <t>49:39.779</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -20048,12 +20087,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>teamWKG</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>01:04:14.441</t>
+          <t>50:08.622</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -20074,19 +20113,19 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01:04:14.441</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>50:08.622</t>
         </is>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -20097,12 +20136,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Talent:frei p/b Baldiso</t>
+          <t>teamWKG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>01:04:18.458</t>
+          <t>01:04:14.441</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -20123,7 +20162,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01:04:18.458</t>
+          <t>01:04:14.441</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -20146,12 +20185,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>Talent:frei p/b Baldiso</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>01:07:19.715</t>
+          <t>01:04:18.458</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -20172,7 +20211,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01:07:19.715</t>
+          <t>01:04:18.458</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -20195,12 +20234,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VCRT</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>01:07:20.310</t>
+          <t>01:07:19.715</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -20221,7 +20260,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01:07:20.310</t>
+          <t>01:07:19.715</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -20244,12 +20283,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>VCRT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>01:07:22.666</t>
+          <t>01:07:20.310</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -20270,7 +20309,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01:07:22.666</t>
+          <t>01:07:20.310</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -20293,12 +20332,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TMA</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>01:07:22.943</t>
+          <t>01:07:22.666</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -20319,7 +20358,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01:07:22.943</t>
+          <t>01:07:22.666</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -20342,12 +20381,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>TMA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>01:11:09.568</t>
+          <t>01:07:22.943</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -20368,7 +20407,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01:11:09.568</t>
+          <t>01:07:22.943</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -20391,12 +20430,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DBR</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>01:12:11.580</t>
+          <t>01:11:09.568</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20417,7 +20456,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01:12:11.580</t>
+          <t>01:11:09.568</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -20435,17 +20474,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>DBR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>07:43:16.590</t>
+          <t>01:12:11.580</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20454,31 +20493,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>01:51:01.890</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>03:25:07.014</t>
+          <t>01:12:11.580</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>02:27:07.686</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -20489,12 +20528,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>01:45:37.540</t>
+          <t>07:43:16.590</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20503,31 +20542,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:51:01.890</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>03:25:07.014</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>01:45:37.540</t>
+          <t>02:27:07.686</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -20538,12 +20577,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RHINO</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>01:45:46.622</t>
+          <t>01:45:37.540</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20556,27 +20595,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>37:38.228</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01:08:08.394</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:45:37.540</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -20587,12 +20626,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Team AHDR</t>
+          <t>RHINO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>01:47:27.893</t>
+          <t>01:45:46.622</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20605,7 +20644,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>36:55.168</t>
+          <t>37:38.228</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -20613,7 +20652,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01:10:32.725</t>
+          <t>01:08:08.394</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -20636,12 +20675,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BikeSurgeon</t>
+          <t>Team AHDR</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>37:03.336</t>
+          <t>01:47:27.893</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20650,11 +20689,11 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>37:03.336</t>
+          <t>36:55.168</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -20662,11 +20701,11 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:10:32.725</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -20685,12 +20724,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>BikeSurgeon</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>38:50.762</t>
+          <t>37:03.336</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20703,7 +20742,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>38:50.762</t>
+          <t>37:03.336</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -20734,12 +20773,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>RuhrRiders</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>39:12.661</t>
+          <t>38:50.762</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -20752,7 +20791,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>39:12.661</t>
+          <t>38:50.762</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20783,12 +20822,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ZCC</t>
+          <t>RuhrRiders</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>39:17.540</t>
+          <t>39:12.661</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -20801,7 +20840,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>39:17.540</t>
+          <t>39:12.661</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -20832,12 +20871,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PTA2</t>
+          <t>ZCC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>39:50.644</t>
+          <t>39:17.540</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -20850,7 +20889,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>39:50.644</t>
+          <t>39:17.540</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -20881,12 +20920,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>PTA2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>40:27.829</t>
+          <t>39:50.644</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -20899,7 +20938,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>40:27.829</t>
+          <t>39:50.644</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -20930,12 +20969,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>41:03.642</t>
+          <t>40:27.829</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -20948,7 +20987,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>41:03.642</t>
+          <t>40:27.829</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -20979,12 +21018,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>41:07.935</t>
+          <t>41:03.642</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -20997,7 +21036,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>41:07.935</t>
+          <t>41:03.642</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -21028,12 +21067,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NewkyBroon</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>41:22.571</t>
+          <t>41:07.935</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -21046,7 +21085,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>41:22.571</t>
+          <t>41:07.935</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -21077,12 +21116,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATP </t>
+          <t>NewkyBroon</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>42:06.313</t>
+          <t>41:22.571</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -21095,7 +21134,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>42:06.313</t>
+          <t>41:22.571</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -21126,12 +21165,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>BIKES &amp;#11088;&amp;#65039;</t>
+          <t xml:space="preserve">ATP </t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>42:13.731</t>
+          <t>42:06.313</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -21144,7 +21183,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>42:13.731</t>
+          <t>42:06.313</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -21175,12 +21214,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BIKES &amp;#11088;&amp;#65039;</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>48:48.863</t>
+          <t>42:13.731</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -21193,11 +21232,11 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>42:13.731</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -21209,11 +21248,11 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>48:48.863</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -21224,12 +21263,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Eintracht Radsport &amp;#129413;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>53:11.906</t>
+          <t>48:48.863</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -21258,7 +21297,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>53:11.906</t>
+          <t>48:48.863</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -21273,12 +21312,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>Eintracht Radsport &amp;#129413;</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>53:14.484</t>
+          <t>53:11.906</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -21307,7 +21346,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>53:14.484</t>
+          <t>53:11.906</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -21322,12 +21361,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CaM</t>
+          <t>MTBtraining</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>01:13:17.611</t>
+          <t>53:14.484</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -21348,35 +21387,35 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01:13:17.611</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>53:14.484</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GTR</t>
+          <t>CaM</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>05:40:35.461</t>
+          <t>01:13:17.611</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -21385,19 +21424,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>01:06:15.485</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>03:26:34.182</t>
+          <t>01:13:17.611</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -21405,11 +21444,11 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>01:07:45.794</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -21420,44 +21459,93 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>GTR</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>05:40:35.461</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>01:06:15.485</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>03:26:34.182</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>01:07:45.794</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>TriLakes</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>51:11.419</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>
       </c>
-      <c r="E142" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>
       </c>
-      <c r="G142" t="n">
+      <c r="G143" t="n">
         <v>0</v>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>
       </c>
-      <c r="I142" t="n">
+      <c r="I143" t="n">
         <v>0</v>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J143" t="inlineStr">
         <is>
           <t>51:11.419</t>
         </is>
       </c>
-      <c r="K142" t="n">
+      <c r="K143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -39480,7 +39568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41591,34 +41679,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6555777</v>
+        <v>810333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Jorge Redondo</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Taeho Kim</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>48:44.964</t>
+          <t>48:40.850</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>5653203</v>
+        <v>5653206</v>
       </c>
     </row>
     <row r="58">
@@ -41629,20 +41713,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4273591</v>
+        <v>6555777</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Karol Borowiak [BH-eRT]</t>
+          <t>Jorge Redondo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BH-eRT</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -41652,45 +41736,49 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>49:59.929</t>
+          <t>48:44.964</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5653204</v>
+        <v>5653203</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>329487</v>
+        <v>4273591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Denis Rombouts</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Karol Borowiak [BH-eRT]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BH-eRT</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>44:53.788</t>
+          <t>49:59.929</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5653202</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="60">
@@ -41701,22 +41789,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8033165</v>
+        <v>329487</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Antonia  [RCC &amp;#128006;/HERC]</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Denis Rombouts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -41724,11 +41808,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45:27.611</t>
+          <t>44:53.788</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="61">
@@ -41739,34 +41823,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5609162</v>
+        <v>8033165</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Alan Robertson</t>
+          <t>Antonia  [RCC &amp;#128006;/HERC]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>45:36.515</t>
+          <t>45:27.611</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>5653203</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="62">
@@ -41777,34 +41861,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1563175</v>
+        <v>5609162</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Alan Robertson</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>45:58.897</t>
+          <t>45:36.515</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>5653202</v>
+        <v>5653203</v>
       </c>
     </row>
     <row r="63">
@@ -41819,11 +41903,11 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2297188</v>
+        <v>1563175</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Javier (HERC) </t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -41833,12 +41917,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>46:40.988</t>
+          <t>45:58.897</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -41857,11 +41941,11 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3083458</v>
+        <v>2297188</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Richard Emblen</t>
+          <t xml:space="preserve">3 Javier (HERC) </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -41871,12 +41955,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>46:49.144</t>
+          <t>46:40.988</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -41891,15 +41975,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2692261</v>
+        <v>3083458</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>Richard Emblen</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -41909,12 +41993,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>46:49.383</t>
+          <t>46:49.144</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -41929,15 +42013,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4698430</v>
+        <v>2692261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Maria ( HERC)</t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -41947,12 +42031,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>46:52.614</t>
+          <t>46:49.383</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -41967,30 +42051,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4698172</v>
+        <v>4698430</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Nigel Morgan</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>Maria ( HERC)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>47:21.350</t>
+          <t>46:52.614</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="68">
@@ -42001,34 +42089,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2470325</v>
+        <v>4698172</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Richard Lutton</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NZBRO </t>
-        </is>
-      </c>
+          <t>Nigel Morgan</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>47:26.701</t>
+          <t>47:21.350</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>5653202</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="69">
@@ -42043,16 +42127,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2445176</v>
+        <v>2470325</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ram&amp;oacute;n S&amp;aacute;nchez Rubio [HISP]</t>
+          <t>Richard Lutton</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t xml:space="preserve">NZBRO </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -42062,11 +42146,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>47:40.294</t>
+          <t>47:26.701</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="70">
@@ -42081,30 +42165,30 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>450573</v>
+        <v>2445176</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karin Lamers (HERC - SRT) </t>
+          <t>Ram&amp;oacute;n S&amp;aacute;nchez Rubio [HISP]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>HISP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>48:07.975</t>
+          <t>47:40.294</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>5653202</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="71">
@@ -42119,30 +42203,30 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>702606</v>
+        <v>450573</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dennis De Poorter </t>
+          <t xml:space="preserve">Karin Lamers (HERC - SRT) </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LTrs</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>48:13.165</t>
+          <t>48:07.975</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5653205</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="72">
@@ -42157,30 +42241,30 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>288798</v>
+        <v>702606</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Scott Henderson (BON - GXY)</t>
+          <t xml:space="preserve">Dennis De Poorter </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>LTrs</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>48:21.000</t>
+          <t>48:13.165</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>5653202</v>
+        <v>5653205</v>
       </c>
     </row>
     <row r="73">
@@ -42195,26 +42279,30 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3532737</v>
+        <v>288798</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jose Javier</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>Scott Henderson (BON - GXY)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>48:27.967</t>
+          <t>48:21.000</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5653205</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="74">
@@ -42229,30 +42317,26 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1379058</v>
+        <v>3532737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Jose Javier</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>48:55.687</t>
+          <t>48:27.967</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5653202</v>
+        <v>5653205</v>
       </c>
     </row>
     <row r="75">
@@ -42263,30 +42347,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3246105</v>
+        <v>6249090</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>David Priest</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>Juan Jose Fondevila</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>BETENDURANCE</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>49:07.073</t>
+          <t>48:46.994</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5653204</v>
+        <v>5653206</v>
       </c>
     </row>
     <row r="76">
@@ -42301,30 +42389,30 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6650098</v>
+        <v>1379058</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kamil Maj</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>49:15.455</t>
+          <t>48:55.687</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="77">
@@ -42339,30 +42427,26 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>574469</v>
+        <v>3246105</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tracy Aldridge-Jones (HERCULES)</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>David Priest</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>49:18.885</t>
+          <t>49:07.073</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>5653202</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="78">
@@ -42377,16 +42461,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1607981</v>
+        <v>6650098</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>John Foley</t>
+          <t>Kamil Maj</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cycling Ireland</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -42396,7 +42480,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>49:39.779</t>
+          <t>49:15.455</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -42415,11 +42499,11 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6513233</v>
+        <v>574469</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Tracy Aldridge-Jones (HERCULES)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -42429,12 +42513,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>49:43.684</t>
+          <t>49:18.885</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -42453,26 +42537,26 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5818155</v>
+        <v>1607981</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Christopher Schwartke</t>
+          <t>John Foley</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
+          <t>Cycling Ireland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>50:08.622</t>
+          <t>49:39.779</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -42491,26 +42575,30 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5922603</v>
+        <v>6513233</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Dmitry Stankevich [MTBtraining]</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t xml:space="preserve">Kim YUU </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>50:26.645</t>
+          <t>49:43.684</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="82">
@@ -42525,26 +42613,26 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3791286</v>
+        <v>5818155</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrew  Black TNP </t>
+          <t>Christopher Schwartke</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t xml:space="preserve">&amp;#128029; KIRCHMAIR e-Cycling </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>50:37.515</t>
+          <t>50:08.622</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -42554,31 +42642,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1417309</v>
+        <v>5922603</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>C hris</t>
+          <t>Dmitry Stankevich [MTBtraining]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>46:22.808</t>
+          <t>50:26.645</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -42588,39 +42676,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6547311</v>
+        <v>3791286</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
+          <t xml:space="preserve">Andrew  Black TNP </t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>48:18.688</t>
+          <t>50:37.515</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>5653202</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="85">
@@ -42631,34 +42719,30 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3789457</v>
+        <v>1417309</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Stuart Williams (TNP)</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>C hris</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>48:48.863</t>
+          <t>46:22.808</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>5653205</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="86">
@@ -42669,15 +42753,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3568483</v>
+        <v>6547311</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>John O  (HERC/EZR)</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -42687,12 +42771,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>48:49.790</t>
+          <t>48:18.688</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -42711,30 +42795,30 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7853050</v>
+        <v>3789457</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>&amp;#9854; Talyn [HERC] &amp;#127487;&amp;#127462;</t>
+          <t>Stuart Williams (TNP)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>49:59.208</t>
+          <t>48:48.863</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5653202</v>
+        <v>5653205</v>
       </c>
     </row>
     <row r="88">
@@ -42749,11 +42833,11 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3089483</v>
+        <v>3568483</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jonathan Hindle</t>
+          <t>John O  (HERC/EZR)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -42768,7 +42852,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>50:58.370</t>
+          <t>48:49.790</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -42787,11 +42871,11 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>832585</v>
+        <v>7853050</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>&amp;#9854; Talyn [HERC] &amp;#127487;&amp;#127462;</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -42801,12 +42885,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>51:01.401</t>
+          <t>49:59.208</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -42821,15 +42905,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4653373</v>
+        <v>3089483</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paul Wa (HERC I)</t>
+          <t>Jonathan Hindle</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -42844,7 +42928,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>51:11.166</t>
+          <t>50:58.370</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -42863,26 +42947,30 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1576625</v>
+        <v>832585</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Data Vader</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>Vonita</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>51:47.878</t>
+          <t>51:01.401</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5653205</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="92">
@@ -42897,11 +42985,11 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2648548</v>
+        <v>4653373</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Paul Wa (HERC I)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -42911,12 +42999,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>52:34.883</t>
+          <t>51:11.166</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -42935,18 +43023,14 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>402420</v>
+        <v>1576625</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ivan Ischia [ITAFT]</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Team Italy</t>
-        </is>
-      </c>
+          <t>Data Vader</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>50+</t>
@@ -42954,11 +43038,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>52:37.876</t>
+          <t>51:47.878</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5653204</v>
+        <v>5653205</v>
       </c>
     </row>
     <row r="94">
@@ -42973,30 +43057,30 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2332799</v>
+        <v>2648548</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Andrea  D@W</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>52:59.664</t>
+          <t>52:34.883</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="95">
@@ -43011,26 +43095,26 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1496021</v>
+        <v>402420</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ralf Breuer [Eintracht]</t>
+          <t>Ivan Ischia [ITAFT]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eintracht Radsport &amp;#129413;</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>53:11.906</t>
+          <t>52:37.876</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -43045,30 +43129,30 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7606805</v>
+        <v>2332799</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Anya Bukharina [MTBtraining]</t>
+          <t>Andrea  D@W</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MTBtraining</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>53:14.484</t>
+          <t>52:59.664</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -43083,30 +43167,34 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2712565</v>
+        <v>1496021</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Barry Rose</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>Ralf Breuer [Eintracht]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Eintracht Radsport &amp;#129413;</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>55:02.720</t>
+          <t>53:11.906</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5653205</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="98">
@@ -43117,34 +43205,34 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>7529924</v>
+        <v>7606805</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Peter Whitelegg&amp;#129385;[HERC]</t>
+          <t>Anya Bukharina [MTBtraining]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>MTBtraining</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>56:23.330</t>
+          <t>53:14.484</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5653202</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="99">
@@ -43159,26 +43247,26 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5639610</v>
+        <v>2712565</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>K ris Res</t>
+          <t>Barry Rose</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>56:58.098</t>
+          <t>55:02.720</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>5653204</v>
+        <v>5653205</v>
       </c>
     </row>
     <row r="100">
@@ -43193,32 +43281,36 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1027344</v>
+        <v>7529924</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Teresa    Webb TN Multisports</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>Peter Whitelegg&amp;#129385;[HERC]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>01:02:04.091</t>
+          <t>56:23.330</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>5653204</v>
+        <v>5653202</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -43227,18 +43319,14 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>127818</v>
+        <v>5639610</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Nick Ske</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>TriLakes</t>
-        </is>
-      </c>
+          <t>K ris Res</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>50+</t>
@@ -43246,7 +43334,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>51:11.419</t>
+          <t>56:58.098</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -43256,7 +43344,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -43265,26 +43353,26 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1645721</v>
+        <v>1027344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Raymond SIMON 1613</t>
+          <t>Teresa    Webb TN Multisports</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>80+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>01:02:17.696</t>
+          <t>01:02:04.091</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5653205</v>
+        <v>5653204</v>
       </c>
     </row>
     <row r="103">
@@ -43299,29 +43387,101 @@
         </is>
       </c>
       <c r="C103" t="n">
+        <v>127818</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Nick Ske</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>TriLakes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>51:11.419</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>5653204</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1645721</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Raymond SIMON 1613</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01:02:17.696</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>5653205</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
         <v>3837944</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>GTR</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>60+</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>01:07:45.794</t>
         </is>
       </c>
-      <c r="H103" t="n">
+      <c r="H105" t="n">
         <v>5653205</v>
       </c>
     </row>

--- a/LaRoja/LaRoja.xlsx
+++ b/LaRoja/LaRoja.xlsx
@@ -6369,7 +6369,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Franz Joop (EVO)</t>
+          <t>Franz Joop (IRN BRU / Chargers)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>3. Fin Stephen (TNP)</t>
+          <t>Fin Stephen (TNP)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14726,12 +14726,16 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>05:40:35.461</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr"/>
+          <t>07:26:20.982</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
       <c r="I375" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="376">
@@ -14941,7 +14945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16415,6 +16419,46 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>04:03:01.203</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3837944</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>07:26:20.982</t>
         </is>
       </c>
     </row>
@@ -25347,7 +25391,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>05:40:35.461</t>
+          <t>07:26:20.982</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25356,7 +25400,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -25384,11 +25428,11 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>01:45:45.521</t>
         </is>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -25516,7 +25560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AD38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29190,6 +29234,104 @@
         <v>18</v>
       </c>
       <c r="AD37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3837944</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>220</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>35.535</v>
+      </c>
+      <c r="I38" t="n">
+        <v>20.203</v>
+      </c>
+      <c r="J38" t="n">
+        <v>36.106</v>
+      </c>
+      <c r="K38" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="L38" t="n">
+        <v>47.638</v>
+      </c>
+      <c r="M38" t="n">
+        <v>46.497</v>
+      </c>
+      <c r="N38" t="n">
+        <v>43.634</v>
+      </c>
+      <c r="O38" t="n">
+        <v>34.543</v>
+      </c>
+      <c r="P38" t="n">
+        <v>35.533</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>40.567</v>
+      </c>
+      <c r="R38" t="n">
+        <v>38.982</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="n">
+        <v>20</v>
+      </c>
+      <c r="U38" t="n">
+        <v>20</v>
+      </c>
+      <c r="V38" t="n">
+        <v>20</v>
+      </c>
+      <c r="W38" t="n">
+        <v>20</v>
+      </c>
+      <c r="X38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29202,7 +29344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30842,6 +30984,50 @@
         <v>14</v>
       </c>
       <c r="L37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3837944</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>622.889</v>
+      </c>
+      <c r="I38" t="n">
+        <v>341.387</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="n">
+        <v>20</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33507,7 +33693,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Franz Joop (EVO)</t>
+          <t>Franz Joop (IRN BRU / Chargers)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -39957,7 +40143,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3. Fin Stephen (TNP)</t>
+          <t>Fin Stephen (TNP)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -41005,7 +41191,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Franz Joop (EVO)</t>
+          <t>Franz Joop (IRN BRU / Chargers)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -41221,7 +41407,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -47234,7 +47420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48416,7 +48602,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -49955,7 +50141,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -51227,6 +51413,44 @@
       </c>
       <c r="H108" t="n">
         <v>5653209</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3837944</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>GTR</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>01:45:45.521</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>5653213</v>
       </c>
     </row>
   </sheetData>

--- a/LaRoja/LaRoja.xlsx
+++ b/LaRoja/LaRoja.xlsx
@@ -1356,7 +1356,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6528902</v>
+        <v>637897</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1365,27 +1365,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>T.J (TNP)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>David Whitfield &amp;#127482;&amp;#127480; &amp;#127482;&amp;#127462;</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01:29:54.366</t>
+          <t>01:26:41.623</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1395,7 +1391,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1844598</v>
+        <v>6528902</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1404,7 +1400,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1414,17 +1410,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sverre Amrani </t>
+          <t>T.J (TNP)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01:36:21.366</t>
+          <t>01:29:54.366</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1434,7 +1430,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2043736</v>
+        <v>1844598</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1443,27 +1439,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">David Serra </t>
+          <t xml:space="preserve">Sverre Amrani </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01:36:22.901</t>
+          <t>01:36:21.366</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1473,7 +1469,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>408391</v>
+        <v>2043736</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1487,22 +1483,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guus Bouman (WAH)</t>
+          <t xml:space="preserve">David Serra </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wahoo Esports</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01:39:04.911</t>
+          <t>01:36:22.901</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1512,7 +1508,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1387591</v>
+        <v>408391</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1526,22 +1522,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tommy Sellars (TFC Typhoon)</t>
+          <t>Guus Bouman (WAH)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>Wahoo Esports</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01:39:09.567</t>
+          <t>01:39:04.911</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1551,7 +1547,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2535432</v>
+        <v>1387591</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1560,7 +1556,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1570,13 +1566,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S t.e.v.e.o.y&amp;trade;</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>Tommy Sellars (TFC Typhoon)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TFC</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01:41:32.274</t>
+          <t>01:39:09.567</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4638424</v>
+        <v>2535432</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1595,27 +1595,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fredi Sonderegger</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EVOLUTION </t>
-        </is>
-      </c>
+          <t>S t.e.v.e.o.y&amp;trade;</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01:46:44.062</t>
+          <t>01:41:32.274</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1625,7 +1621,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15354</v>
+        <v>4638424</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jokim Pluijmers</t>
+          <t>Fredi Sonderegger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1654,17 +1650,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>31:51.823</t>
+          <t>01:46:44.062</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6169388</v>
+        <v>15354</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1673,27 +1669,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wib Wob</t>
+          <t>Jokim Pluijmers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t xml:space="preserve">EVOLUTION </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>31:52.039</t>
+          <t>31:51.823</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1703,7 +1699,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>204625</v>
+        <v>6169388</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1712,7 +1708,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1722,17 +1718,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eugene Conradie | EVOLVE</t>
+          <t>Wib Wob</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EVOLVE</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31:52.680</t>
+          <t>31:52.039</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1742,7 +1738,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5687025</v>
+        <v>204625</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1756,22 +1752,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jonas Grunau</t>
+          <t>Eugene Conradie | EVOLVE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>EVOLVE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>32:34.794</t>
+          <t>31:52.680</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1781,7 +1777,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5126490</v>
+        <v>5687025</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1795,18 +1791,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ruben Silva</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>Jonas Grunau</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32:34.932</t>
+          <t>32:34.794</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4379470</v>
+        <v>5126490</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1825,23 +1825,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jonny Oparka</t>
+          <t>Ruben Silva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>32:35.010</t>
+          <t>32:34.932</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4730842</v>
+        <v>4379470</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1870,17 +1870,13 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>ATGNI</t>
-        </is>
-      </c>
+          <t>Jonny Oparka</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>32:35.529</t>
+          <t>32:35.010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1890,7 +1886,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>902451</v>
+        <v>4730842</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1904,22 +1900,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>P. Holzmann</t>
+          <t>Harris Waters(ATGNI)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>&amp;#128692;&amp;#127996;&amp;zwj;&amp;#9794;&amp;#65039;WLBB&amp;#127867;</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>32:36.425</t>
+          <t>32:35.529</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1929,7 +1925,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7624931</v>
+        <v>902451</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1943,18 +1939,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magnus Krog</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>P. Holzmann</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>&amp;#128692;&amp;#127996;&amp;zwj;&amp;#9794;&amp;#65039;WLBB&amp;#127867;</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>32:36.635</t>
+          <t>32:36.425</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>203138</v>
+        <v>7624931</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1978,18 +1978,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>michael koutouzov</t>
+          <t>Magnus Krog</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>32:37.139</t>
+          <t>32:36.635</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1020762</v>
+        <v>203138</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2008,23 +2008,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jeff Crystal</t>
+          <t>michael koutouzov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>32:39.260</t>
+          <t>32:37.139</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>859376</v>
+        <v>1020762</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2043,27 +2043,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marcel Hies</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>LEVEL Esports</t>
-        </is>
-      </c>
+          <t>Jeff Crystal</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>33:00.337</t>
+          <t>32:39.260</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2073,7 +2069,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>99549</v>
+        <v>859376</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2082,27 +2078,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norman Henderson (CRYO-GEN)</t>
+          <t>Marcel Hies</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>33:00.607</t>
+          <t>33:00.337</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2112,7 +2108,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4860176</v>
+        <v>99549</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2121,27 +2117,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mads Buster</t>
+          <t>Norman Henderson (CRYO-GEN)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>Team CRYO-GEN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>33:04.560</t>
+          <t>33:00.607</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2151,7 +2147,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5252523</v>
+        <v>4860176</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2165,22 +2161,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tony  Delogne (WATT) </t>
+          <t>Mads Buster</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33:04.890</t>
+          <t>33:04.560</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2190,7 +2186,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6604424</v>
+        <v>5252523</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2199,27 +2195,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Michael O Donoghue</t>
+          <t xml:space="preserve">Tony  Delogne (WATT) </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>33:05.206</t>
+          <t>33:04.890</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2229,7 +2225,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5231519</v>
+        <v>6604424</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2243,22 +2239,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jason Taylor [ITA | CN]</t>
+          <t>Michael O Donoghue</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>33:05.642</t>
+          <t>33:05.206</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2268,7 +2264,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3846291</v>
+        <v>5231519</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2282,18 +2278,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JULIO MG</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>Jason Taylor [ITA | CN]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>33:05.695</t>
+          <t>33:05.642</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4010970</v>
+        <v>3846291</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2317,18 +2317,18 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>YU SUE</t>
+          <t>JULIO MG</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>34:04.596</t>
+          <t>33:05.695</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4474215</v>
+        <v>4010970</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2357,17 +2357,13 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Adrian Christie&amp;#128007;</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Team CRYO-GEN</t>
-        </is>
-      </c>
+          <t>YU SUE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>34:05.635</t>
+          <t>34:04.596</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2377,7 +2373,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>747912</v>
+        <v>4474215</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2386,17 +2382,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Simon Cochrane (CRYO RDT Vultures)</t>
+          <t>Adrian Christie&amp;#128007;</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2406,7 +2402,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>34:09.504</t>
+          <t>34:05.635</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2416,7 +2412,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4777894</v>
+        <v>747912</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2425,7 +2421,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2435,13 +2431,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brian Leakey</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>Simon Cochrane (CRYO RDT Vultures)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Team CRYO-GEN</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>34:35.592</t>
+          <t>34:09.504</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1380824</v>
+        <v>4777894</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2460,27 +2460,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Joris Van Hootegem</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>HMB</t>
-        </is>
-      </c>
+          <t>Brian Leakey</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>35:04.535</t>
+          <t>34:35.592</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2490,7 +2486,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4934904</v>
+        <v>1380824</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2499,27 +2495,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>romain urnel RCC. TOKYO&amp;#127471;&amp;#127477;</t>
+          <t>Joris Van Hootegem</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rapha_RCC</t>
+          <t>HMB</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>35:35.345</t>
+          <t>35:04.535</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2529,7 +2525,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4966352</v>
+        <v>4934904</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2538,23 +2534,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gabriel Pattee</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>romain urnel RCC. TOKYO&amp;#127471;&amp;#127477;</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rapha_RCC</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>36:05.168</t>
+          <t>35:35.345</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3809672</v>
+        <v>4966352</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2573,27 +2573,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>David Liberato</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>TugaZ</t>
-        </is>
-      </c>
+          <t>Gabriel Pattee</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>36:54.174</t>
+          <t>36:05.168</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2603,7 +2599,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>551676</v>
+        <v>3809672</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2622,13 +2618,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sean Dailey </t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>David Liberato</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>TugaZ</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>37:12.560</t>
+          <t>36:54.174</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1267806</v>
+        <v>551676</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2657,17 +2657,13 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Joe Senn</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>ABR Cycle Team</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Sean Dailey </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>37:26.653</t>
+          <t>37:12.560</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2677,7 +2673,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>666778</v>
+        <v>1267806</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2696,17 +2692,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paolo Estar (ZSUNR)</t>
+          <t>Joe Senn</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>ABR Cycle Team</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>37:26.993</t>
+          <t>37:26.653</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2716,7 +2712,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1439458</v>
+        <v>666778</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2730,22 +2726,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Daniel Anderson (RtB)</t>
+          <t>Paolo Estar (ZSUNR)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>37:27.116</t>
+          <t>37:26.993</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2755,7 +2751,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>679773</v>
+        <v>1439458</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2769,22 +2765,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padraic OFlynn </t>
+          <t>Daniel Anderson (RtB)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>37:27.795</t>
+          <t>37:27.116</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2794,7 +2790,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>7820316</v>
+        <v>679773</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2813,17 +2809,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JB Villatte [GVRL]</t>
+          <t xml:space="preserve">Padraic OFlynn </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>37:27.838</t>
+          <t>37:27.795</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -2833,7 +2829,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>325918</v>
+        <v>7820316</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2842,7 +2838,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2852,17 +2848,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Matt Stan</t>
+          <t>JB Villatte [GVRL]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PainCavesHeroes</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>37:29.331</t>
+          <t>37:27.838</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -2872,7 +2868,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1239968</v>
+        <v>325918</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2881,7 +2877,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2891,13 +2887,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JOKER&amp;#128520;</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>Matt Stan</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PainCavesHeroes</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>37:29.639</t>
+          <t>37:29.331</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>310675</v>
+        <v>1239968</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2916,27 +2916,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Philip Landstrom</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>SZ</t>
-        </is>
-      </c>
+          <t>JOKER&amp;#128520;</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>37:29.957</t>
+          <t>37:29.639</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -2946,7 +2942,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5969352</v>
+        <v>310675</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2955,7 +2951,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2965,13 +2961,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mike Amyotte</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>Philip Landstrom</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SZ</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>38:23.638</t>
+          <t>37:29.957</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2981,7 +2981,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125622</v>
+        <v>5969352</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2995,22 +2995,18 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tim Cartwright</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>KISS RT</t>
-        </is>
-      </c>
+          <t>Mike Amyotte</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>38:26.114</t>
+          <t>38:23.638</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -3020,7 +3016,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1323698</v>
+        <v>125622</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3039,17 +3035,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KENJI ITO[ZEAL]</t>
+          <t>Tim Cartwright</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ZEAL</t>
+          <t>KISS RT</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>38:26.813</t>
+          <t>38:26.114</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3059,7 +3055,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7552376</v>
+        <v>1323698</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3078,13 +3074,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HaG TaK</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>KENJI ITO[ZEAL]</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ZEAL</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>38:30.466</t>
+          <t>38:26.813</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>5885126</v>
+        <v>7552376</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3103,23 +3103,23 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vadim K.</t>
+          <t>HaG TaK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>38:39.490</t>
+          <t>38:30.466</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6052283</v>
+        <v>5885126</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3143,18 +3143,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Henning S&amp;oslash;ndergaard</t>
+          <t>Vadim K.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>38:59.026</t>
+          <t>38:39.490</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>972868</v>
+        <v>6052283</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3183,13 +3183,13 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>&amp;#12471;&amp;#12517;&amp;#12460;&amp;#12540;&amp;#24215;&amp;#38263; &amp;#12288;BICYCLESTEP/ZEAL</t>
+          <t>Henning S&amp;oslash;ndergaard</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>39:01.361</t>
+          <t>38:59.026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3044689</v>
+        <v>972868</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3218,17 +3218,13 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yassine Sissi</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>&amp;#12471;&amp;#12517;&amp;#12460;&amp;#12540;&amp;#24215;&amp;#38263; &amp;#12288;BICYCLESTEP/ZEAL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>39:08.618</t>
+          <t>39:01.361</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3238,7 +3234,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>25864</v>
+        <v>3044689</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3247,27 +3243,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Michael Mansfield</t>
+          <t>Yassine Sissi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>39:08.645</t>
+          <t>39:08.618</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3277,7 +3273,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3605728</v>
+        <v>25864</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3286,7 +3282,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3296,17 +3292,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Steven Garr&amp;eacute; [WATT]</t>
+          <t>Michael Mansfield</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>Team CRYO-GEN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>39:08.656</t>
+          <t>39:08.645</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3316,7 +3312,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1119043</v>
+        <v>3605728</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3325,27 +3321,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hywel Davies</t>
+          <t>Steven Garr&amp;eacute; [WATT]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wahoo Esports</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>39:08.932</t>
+          <t>39:08.656</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3355,7 +3351,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>6954297</v>
+        <v>1119043</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3369,18 +3365,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dario Manzonetti</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
+          <t>Hywel Davies</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Wahoo Esports</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>39:09.173</t>
+          <t>39:08.932</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1983819</v>
+        <v>6954297</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3409,17 +3409,13 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Julien Hoeksema (FFZ)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>FFZ</t>
-        </is>
-      </c>
+          <t>Dario Manzonetti</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>39:10.966</t>
+          <t>39:09.173</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -3429,7 +3425,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1831460</v>
+        <v>1983819</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3438,27 +3434,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GOYO Almazan(Dirt)</t>
+          <t>Julien Hoeksema (FFZ)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>FFZ</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>39:11.595</t>
+          <t>39:10.966</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3468,7 +3464,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1243441</v>
+        <v>1831460</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3477,27 +3473,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Victor Vaz [TugaZ]</t>
+          <t>GOYO Almazan(Dirt)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TugaZ</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>39:14.655</t>
+          <t>39:11.595</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3507,7 +3503,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>401837</v>
+        <v>1243441</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3516,27 +3512,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuba Sztanderski [mTNT] </t>
+          <t>Victor Vaz [TugaZ]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>mTNT</t>
+          <t>TugaZ</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>39:14.728</t>
+          <t>39:14.655</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3546,7 +3542,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3947070</v>
+        <v>401837</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3555,27 +3551,27 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tom Coleman (Mersey ZRG)</t>
+          <t xml:space="preserve">Kuba Sztanderski [mTNT] </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mersey ZRG </t>
+          <t>mTNT</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>39:14.741</t>
+          <t>39:14.728</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3585,7 +3581,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2133020</v>
+        <v>3947070</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3594,27 +3590,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Thomas Grill (TSE)</t>
+          <t>Tom Coleman (Mersey ZRG)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t xml:space="preserve">Mersey ZRG </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>39:31.659</t>
+          <t>39:14.741</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3624,7 +3620,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5401313</v>
+        <v>2133020</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3638,22 +3634,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Henric Derneg&amp;aring;rd [SZ]</t>
+          <t>Thomas Grill (TSE)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>39:32.046</t>
+          <t>39:31.659</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3663,7 +3659,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2570898</v>
+        <v>5401313</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3677,18 +3673,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Patrick Vanden Eede</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>Henric Derneg&amp;aring;rd [SZ]</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SZ</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>39:32.276</t>
+          <t>39:32.046</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>6979356</v>
+        <v>2570898</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3707,23 +3707,23 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shutaro Izumida</t>
+          <t>Patrick Vanden Eede</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>40:12.145</t>
+          <t>39:32.276</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1716096</v>
+        <v>6979356</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3742,27 +3742,23 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aaron Girdlestone (RELENTLESS)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>RELENTLESS</t>
-        </is>
-      </c>
+          <t>Shutaro Izumida</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>40:14.294</t>
+          <t>40:12.145</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -3772,7 +3768,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1257407</v>
+        <v>1716096</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3781,27 +3777,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kalle Kadens</t>
+          <t>Aaron Girdlestone (RELENTLESS)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>RELENTLESS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>40:17.196</t>
+          <t>40:14.294</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -3811,7 +3807,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>5985571</v>
+        <v>1257407</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3820,23 +3816,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wil Murray</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>Kalle Kadens</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>OTR Racing</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>40:17.419</t>
+          <t>40:17.196</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>845809</v>
+        <v>5985571</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3865,17 +3865,13 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Matthew Fisher (Sussex Revolution VC - B)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>SRVC</t>
-        </is>
-      </c>
+          <t>Wil Murray</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>40:21.028</t>
+          <t>40:17.419</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -3885,7 +3881,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>616981</v>
+        <v>845809</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3894,7 +3890,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3904,17 +3900,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mike  Cuming (Saris | Nopinz)</t>
+          <t>Matthew Fisher (Sussex Revolution VC - B)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SARIS</t>
+          <t>SRVC</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>40:24.111</t>
+          <t>40:21.028</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -3924,7 +3920,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2103662</v>
+        <v>616981</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3933,27 +3929,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>J Jansen</t>
+          <t>Mike  Cuming (Saris | Nopinz)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RWCAhoy</t>
+          <t>SARIS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>40:32.022</t>
+          <t>40:24.111</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -3963,7 +3959,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>290969</v>
+        <v>2103662</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3977,22 +3973,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>jean mespoulede[NOAQ]</t>
+          <t>J Jansen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NOAQ</t>
+          <t>RWCAhoy</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>40:33.089</t>
+          <t>40:32.022</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4002,7 +3998,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>793757</v>
+        <v>290969</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4011,23 +4007,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>U23</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Caleb Johnstone</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>jean mespoulede[NOAQ]</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NOAQ</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>40:33.783</t>
+          <t>40:33.089</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1701862</v>
+        <v>793757</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4046,23 +4046,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rob Sales </t>
+          <t>Caleb Johnstone</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>40:33.869</t>
+          <t>40:33.783</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3189643</v>
+        <v>1701862</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4086,22 +4086,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Joris Bos</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>DD&amp;#129414; &amp; C&amp;#128036;&amp;#128036;&amp;#128036;</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Rob Sales </t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>40:35.410</t>
+          <t>40:33.869</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4111,7 +4107,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>398934</v>
+        <v>3189643</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4120,27 +4116,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Eelco Zonruiter</t>
+          <t>Joris Bos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>de_tempobeukers</t>
+          <t>DD&amp;#129414; &amp; C&amp;#128036;&amp;#128036;&amp;#128036;</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>40:38.855</t>
+          <t>40:35.410</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4150,7 +4146,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>452156</v>
+        <v>398934</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4164,22 +4160,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brian Duffy Jr | NeXT pb Enshored</t>
+          <t>Eelco Zonruiter</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NeXT pb ENSH</t>
+          <t>de_tempobeukers</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>40:51.876</t>
+          <t>40:38.855</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4189,7 +4185,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>197937</v>
+        <v>452156</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4203,22 +4199,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Roy Roesthuis (OWC)</t>
+          <t>Brian Duffy Jr | NeXT pb Enshored</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ZSUNR</t>
+          <t>NeXT pb ENSH</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>41:02.101</t>
+          <t>40:51.876</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -4228,7 +4224,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>15522</v>
+        <v>197937</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4247,17 +4243,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Michael Podzaline [X] (Wahoo Le Col)</t>
+          <t>Roy Roesthuis (OWC)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wahoo Esports</t>
+          <t>ZSUNR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>41:05.521</t>
+          <t>41:02.101</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4267,7 +4263,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4581862</v>
+        <v>15522</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4276,27 +4272,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Alexander Stabij</t>
+          <t>Michael Podzaline [X] (Wahoo Le Col)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Wahoo Esports</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>41:06.722</t>
+          <t>41:05.521</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -4306,7 +4302,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1193473</v>
+        <v>4581862</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4315,7 +4311,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4325,17 +4321,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tatsuya Yokoi[EMU SHIMAUMA]</t>
+          <t>Alexander Stabij</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>EMU</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>41:10.492</t>
+          <t>41:06.722</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -4345,7 +4341,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1175748</v>
+        <v>1193473</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4354,27 +4350,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jos Castelijns(TeamNL)</t>
+          <t>Tatsuya Yokoi[EMU SHIMAUMA]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TeamNL</t>
+          <t>EMU</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>41:11.950</t>
+          <t>41:10.492</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -4384,7 +4380,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4254740</v>
+        <v>1175748</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -4393,23 +4389,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>T     Tobita(3UP)</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
+          <t>Jos Castelijns(TeamNL)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>TeamNL</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>41:16.007</t>
+          <t>41:11.950</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -4419,7 +4419,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1024808</v>
+        <v>4254740</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4433,18 +4433,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>The_Fast_Life</t>
+          <t>T     Tobita(3UP)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>41:16.249</t>
+          <t>41:16.007</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>20119</v>
+        <v>1024808</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4473,17 +4473,13 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brian Owens</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>The_Fast_Life</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>41:16.391</t>
+          <t>41:16.249</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -4493,7 +4489,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7308408</v>
+        <v>20119</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4507,22 +4503,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Preston Fonseca</t>
+          <t>Brian Owens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Havoq</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>41:16.717</t>
+          <t>41:16.391</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -4532,7 +4528,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>553721</v>
+        <v>7308408</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4541,23 +4537,27 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Meta P</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>Preston Fonseca</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Havoq</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>41:18.064</t>
+          <t>41:16.717</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>8262983</v>
+        <v>553721</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4586,17 +4586,13 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tuco  Benedicto (TEZH)</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>TEZH Racing</t>
-        </is>
-      </c>
+          <t>Meta P</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>41:24.223</t>
+          <t>41:18.064</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -4606,7 +4602,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4394601</v>
+        <v>8262983</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4615,23 +4611,27 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Christoffer Ponikowski</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
+          <t>Tuco  Benedicto (TEZH)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>TEZH Racing</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>41:33.751</t>
+          <t>41:24.223</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>211779</v>
+        <v>4394601</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -4650,23 +4650,23 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Luke Smith #whytebikes</t>
+          <t>Christoffer Ponikowski</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>41:41.474</t>
+          <t>41:33.751</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>368243</v>
+        <v>211779</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4695,17 +4695,13 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Scott Gavens (Galaxy / ADHR)</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Luke Smith #whytebikes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>41:49.934</t>
+          <t>41:41.474</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -4715,7 +4711,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3147317</v>
+        <v>368243</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -4734,13 +4730,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan pugh </t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>Scott Gavens (Galaxy / ADHR)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>41:49.935</t>
+          <t>41:49.934</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6813660</v>
+        <v>3147317</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4769,13 +4769,13 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Christophe Ondet</t>
+          <t xml:space="preserve">Jonathan pugh </t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>41:55.713</t>
+          <t>41:49.935</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2030298</v>
+        <v>6813660</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4804,17 +4804,13 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Erik John (TFC)</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>TFC</t>
-        </is>
-      </c>
+          <t>Christophe Ondet</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>42:05.867</t>
+          <t>41:55.713</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -4824,7 +4820,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6715306</v>
+        <v>2030298</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4838,22 +4834,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jay Rowe</t>
+          <t>Erik John (TFC)</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>42:17.793</t>
+          <t>42:05.867</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -4863,7 +4859,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5819390</v>
+        <v>6715306</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4872,7 +4868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4882,17 +4878,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paulo Ramos</t>
+          <t>Jay Rowe</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PainCavesHeroes</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>42:32.614</t>
+          <t>42:17.793</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -4902,7 +4898,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1592926</v>
+        <v>5819390</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4911,27 +4907,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radoslav SzFFWD</t>
+          <t>Paulo Ramos</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>PainCavesHeroes</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>42:42.823</t>
+          <t>42:32.614</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -4941,7 +4937,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>3071349</v>
+        <v>1592926</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4955,12 +4951,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shane O&amp;#039;Flynn (RWB SerrBanos)</t>
+          <t>Radoslav SzFFWD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4970,7 +4966,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>43:13.584</t>
+          <t>42:42.823</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -4980,7 +4976,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>226811</v>
+        <v>3071349</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4989,27 +4985,27 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Adam Gascoigne</t>
+          <t>Shane O&amp;#039;Flynn (RWB SerrBanos)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>43:17.305</t>
+          <t>43:13.584</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -5019,7 +5015,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>54406</v>
+        <v>226811</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -5028,27 +5024,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kevin Horsley &amp;#128052;</t>
+          <t>Adam Gascoigne</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wahoo Esports</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>43:21.716</t>
+          <t>43:17.305</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -5058,7 +5054,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>7484167</v>
+        <v>54406</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -5067,27 +5063,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Edmund Tang</t>
+          <t>Kevin Horsley &amp;#128052;</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Wahoo Esports</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>43:43.562</t>
+          <t>43:21.716</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -5097,7 +5093,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>442300</v>
+        <v>7484167</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -5106,23 +5102,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dan Hedges &amp;#128062;&amp;#129312;</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>Edmund Tang</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>44:13.428</t>
+          <t>43:43.562</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2299569</v>
+        <v>442300</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5141,23 +5141,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Blue &amp;#12354;&amp;#12362;&amp;#12367;&amp;#12394;&amp;#12356;&amp;#12369;&amp;#12393;</t>
+          <t>Dan Hedges &amp;#128062;&amp;#129312;</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>44:50.285</t>
+          <t>44:13.428</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1813196</v>
+        <v>2299569</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -5181,22 +5181,18 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jordi Riu @YT (TEZH)</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>TEZH Racing</t>
-        </is>
-      </c>
+          <t>Blue &amp;#12354;&amp;#12362;&amp;#12367;&amp;#12394;&amp;#12356;&amp;#12369;&amp;#12393;</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>45:14.252</t>
+          <t>44:50.285</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -5206,7 +5202,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>637897</v>
+        <v>1813196</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -5215,23 +5211,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>David Whitfield &amp;#127482;&amp;#127480; &amp;#127482;&amp;#127462;</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
+          <t>Jordi Riu @YT (TEZH)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>TEZH Racing</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>45:30.407</t>
+          <t>45:14.252</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -19081,7 +19081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20724,30 +20724,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4254740</v>
+        <v>637897</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T     Tobita(3UP)</t>
+          <t>David Whitfield &amp;#127482;&amp;#127480; &amp;#127482;&amp;#127462;</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41:16.007</t>
+          <t>41:11.216</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5653218</v>
+        <v>5653219</v>
       </c>
     </row>
     <row r="46">
@@ -20762,22 +20762,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1024808</v>
+        <v>4254740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The_Fast_Life</t>
+          <t>T     Tobita(3UP)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>41:16.249</t>
+          <t>41:16.007</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -20796,18 +20796,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20119</v>
+        <v>1024808</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Brian Owens</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>The_Fast_Life</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -20815,7 +20811,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>41:16.391</t>
+          <t>41:16.249</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -20834,26 +20830,26 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7308408</v>
+        <v>20119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Preston Fonseca</t>
+          <t>Brian Owens</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Havoq</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>41:16.717</t>
+          <t>41:16.391</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -20868,26 +20864,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>553721</v>
+        <v>7308408</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Meta P</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>Preston Fonseca</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Havoq</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>41:18.064</t>
+          <t>41:16.717</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -20902,22 +20902,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>368243</v>
+        <v>553721</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Scott Gavens (Galaxy / ADHR)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[GALAXY]</t>
-        </is>
-      </c>
+          <t>Meta P</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -20925,11 +20921,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>41:49.934</t>
+          <t>41:18.064</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="51">
@@ -20944,14 +20940,18 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3147317</v>
+        <v>368243</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan pugh </t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>Scott Gavens (Galaxy / ADHR)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>[GALAXY]</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -20959,11 +20959,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>41:49.935</t>
+          <t>41:49.934</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5653216</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="52">
@@ -20978,18 +20978,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7533529</v>
+        <v>3147317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>dwaine henderson</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Jonathan pugh </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -20997,11 +20993,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>42:04.057</t>
+          <t>41:49.935</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5653217</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="53">
@@ -21016,16 +21012,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2030298</v>
+        <v>7533529</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erik John (TFC)</t>
+          <t>dwaine henderson</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -21035,11 +21031,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>42:05.867</t>
+          <t>42:04.057</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>5653218</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="54">
@@ -21050,30 +21046,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2881246</v>
+        <v>2030298</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Liam  Donnelly (TriveloCoaching)</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>Erik John (TFC)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TFC</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>42:37.226</t>
+          <t>42:05.867</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="55">
@@ -21084,34 +21084,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1592926</v>
+        <v>2881246</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Radoslav SzFFWD</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Team RWB</t>
-        </is>
-      </c>
+          <t>Liam  Donnelly (TriveloCoaching)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>42:42.823</t>
+          <t>42:37.226</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="56">
@@ -21122,20 +21118,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>784914</v>
+        <v>1592926</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Seb &amp;#129302;&amp;#129421;</t>
+          <t>Radoslav SzFFWD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beastmode</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -21145,11 +21141,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>42:51.632</t>
+          <t>42:42.823</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5653216</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="57">
@@ -21160,30 +21156,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3071349</v>
+        <v>784914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Shane O&amp;#039;Flynn (RWB SerrBanos)</t>
+          <t>Seb &amp;#129302;&amp;#129421;</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>Beastmode</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>43:13.584</t>
+          <t>42:51.632</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -21202,26 +21198,26 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>210667</v>
+        <v>3071349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kristian Kr&amp;oslash;ll</t>
+          <t>Shane O&amp;#039;Flynn (RWB SerrBanos)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FUSION ECT Masters</t>
+          <t>Team RWB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>47:06.762</t>
+          <t>43:13.584</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -21231,39 +21227,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3513060</v>
+        <v>210667</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas  Japp </t>
+          <t>Kristian Kr&amp;oslash;ll</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Japp</t>
+          <t>FUSION ECT Masters</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>39:45.889</t>
+          <t>47:06.762</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="60">
@@ -21274,26 +21270,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>247483</v>
+        <v>3513060</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>k quinone</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t xml:space="preserve">Thomas  Japp </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Japp</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>40:08.398</t>
+          <t>39:45.889</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -21312,18 +21312,14 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3239205</v>
+        <v>247483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Marc Jansen</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>WTCM</t>
-        </is>
-      </c>
+          <t>k quinone</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -21331,7 +21327,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>40:09.211</t>
+          <t>40:08.398</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -21350,26 +21346,26 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1005102</v>
+        <v>3239205</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Marc Jansen</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>WTCM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>40:09.679</t>
+          <t>40:09.211</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -21388,26 +21384,26 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3231133</v>
+        <v>1005102</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Izra Valenzuela</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>40:13.589</t>
+          <t>40:09.679</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -21426,26 +21422,26 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1488791</v>
+        <v>3231133</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sandro Stra&amp;szlig;er [EVO]</t>
+          <t>Izra Valenzuela</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>40:25.426</t>
+          <t>40:13.589</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -21464,14 +21460,18 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5973061</v>
+        <v>1488791</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Pawe&amp;#322; Potocki</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>Sandro Stra&amp;szlig;er [EVO]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -21479,11 +21479,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>40:32.413</t>
+          <t>40:25.426</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="66">
@@ -21498,18 +21498,14 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5500742</v>
+        <v>5973061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ward De Schryver (WATT)</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>The Watt Squad</t>
-        </is>
-      </c>
+          <t>Pawe&amp;#322; Potocki</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -21517,7 +21513,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>40:32.806</t>
+          <t>40:32.413</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -21536,16 +21532,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>44424</v>
+        <v>5500742</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Rasmus Raben</t>
+          <t>Ward De Schryver (WATT)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ABR Cycle Team</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -21555,7 +21551,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>40:33.026</t>
+          <t>40:32.806</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -21570,34 +21566,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>918258</v>
+        <v>44424</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN JIMENEZ [5.W.4.T] </t>
+          <t>Rasmus Raben</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>5.W.4.T</t>
+          <t>ABR Cycle Team</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>41:16.784</t>
+          <t>40:33.026</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>5653218</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="69">
@@ -21612,16 +21608,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2488343</v>
+        <v>918258</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Dan Ward-Smith (EVO)</t>
+          <t xml:space="preserve">JUAN JIMENEZ [5.W.4.T] </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVOLUTION </t>
+          <t>5.W.4.T</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -21631,11 +21627,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>41:29.682</t>
+          <t>41:16.784</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="70">
@@ -21646,18 +21642,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5786822</v>
+        <v>2488343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Chris Tuckey [DGG]</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>Dan Ward-Smith (EVO)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EVOLUTION </t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>41:30.623</t>
+          <t>41:29.682</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -21680,22 +21680,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4133292</v>
+        <v>5786822</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Michael Zagar</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>HKCC</t>
-        </is>
-      </c>
+          <t>Chris Tuckey [DGG]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -21703,7 +21699,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>41:33.050</t>
+          <t>41:30.623</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -21718,30 +21714,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1332978</v>
+        <v>4133292</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Angela MacRae [HERC]</t>
+          <t>Michael Zagar</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>HKCC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>41:34.357</t>
+          <t>41:33.050</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -21760,26 +21756,26 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1236596</v>
+        <v>1332978</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Neil Rogers</t>
+          <t>Angela MacRae [HERC]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>41:34.401</t>
+          <t>41:34.357</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -21798,16 +21794,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1525003</v>
+        <v>1236596</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greg Morgan </t>
+          <t>Neil Rogers</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -21817,7 +21813,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>41:34.451</t>
+          <t>41:34.401</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -21836,16 +21832,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4567741</v>
+        <v>1525003</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Andy Buclaw [CN!D]</t>
+          <t xml:space="preserve">Greg Morgan </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CONED</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -21855,11 +21851,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>42:01.790</t>
+          <t>41:34.451</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="76">
@@ -21874,16 +21870,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7344297</v>
+        <v>4567741</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mikkel B&amp;oslash;gebjerg (D&amp;AElig;C)</t>
+          <t>Andy Buclaw [CN!D]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>D&amp;AElig;C</t>
+          <t>CONED</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -21893,11 +21889,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>42:03.652</t>
+          <t>42:01.790</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>5653217</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="77">
@@ -21912,26 +21908,30 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>335353</v>
+        <v>7344297</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Benjamin Chin-Yee</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>Mikkel B&amp;oslash;gebjerg (D&amp;AElig;C)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>D&amp;AElig;C</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>42:11.426</t>
+          <t>42:03.652</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>5653216</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="78">
@@ -21946,18 +21946,14 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1537868</v>
+        <v>335353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Benjamin Walpot</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>BZR eCycling Club</t>
-        </is>
-      </c>
+          <t>Benjamin Chin-Yee</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -21965,7 +21961,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>42:13.062</t>
+          <t>42:11.426</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -21984,26 +21980,26 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3062442</v>
+        <v>1537868</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>S&amp;eacute;bastien  ducasse (FFZ)</t>
+          <t>Benjamin Walpot</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FFZ</t>
+          <t>BZR eCycling Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>42:13.174</t>
+          <t>42:13.062</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -22022,26 +22018,26 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7843033</v>
+        <v>3062442</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Oli Toth (RtB)</t>
+          <t>S&amp;eacute;bastien  ducasse (FFZ)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RtB</t>
+          <t>FFZ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>42:13.794</t>
+          <t>42:13.174</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -22060,30 +22056,30 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9152</v>
+        <v>7843033</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Simon Baker</t>
+          <t>Oli Toth (RtB)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>RtB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>42:21.151</t>
+          <t>42:13.794</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>5653215</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="82">
@@ -22098,30 +22094,30 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2984324</v>
+        <v>9152</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Peter Fohr4390</t>
+          <t>Simon Baker</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ZRG</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>42:24.990</t>
+          <t>42:21.151</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5653216</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="83">
@@ -22132,34 +22128,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2881429</v>
+        <v>2984324</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+          <t>Peter Fohr4390</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>ZRG</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>42:38.836</t>
+          <t>42:24.990</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="84">
@@ -22174,11 +22170,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>260262</v>
+        <v>2881429</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Greg SHED</t>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -22188,12 +22184,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>42:38.953</t>
+          <t>42:38.836</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -22212,22 +22208,26 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4166463</v>
+        <v>260262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>Greg SHED</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>42:40.424</t>
+          <t>42:38.953</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -22242,26 +22242,26 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7443223</v>
+        <v>4166463</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Zoe Tucker</t>
+          <t>Corey Green (YT) GarageCycling</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>42:45.542</t>
+          <t>42:40.424</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -22280,26 +22280,26 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5675805</v>
+        <v>7443223</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jesper Bertelsen</t>
+          <t>Zoe Tucker</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>42:58.972</t>
+          <t>42:45.542</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="88">
@@ -22310,34 +22310,30 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5402473</v>
+        <v>5675805</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>geoffrey boyd</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Jesper Bertelsen</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>43:18.029</t>
+          <t>42:58.972</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5653218</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="89">
@@ -22348,18 +22344,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>447765</v>
+        <v>5402473</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>show3 kogaaaaa</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>geoffrey boyd</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>43:20.203</t>
+          <t>43:18.029</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -22386,30 +22386,26 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3785513</v>
+        <v>447765</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Chris Beardsell (TNP)</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>show3 kogaaaaa</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>43:20.400</t>
+          <t>43:20.203</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5653216</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="91">
@@ -22424,26 +22420,26 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>198785</v>
+        <v>3785513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Deirdre Maloney</t>
+          <t>Chris Beardsell (TNP)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HGR</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>43:57.444</t>
+          <t>43:20.400</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -22462,16 +22458,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>297113</v>
+        <v>198785</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erik van Lakerveld</t>
+          <t>Deirdre Maloney</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SWABO</t>
+          <t>HGR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -22481,11 +22477,11 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>44:07.063</t>
+          <t>43:57.444</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="93">
@@ -22496,20 +22492,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3105882</v>
+        <v>297113</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tom Rose</t>
+          <t>Erik van Lakerveld</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JURASPORTS</t>
+          <t>SWABO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -22519,11 +22515,11 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>44:10.033</t>
+          <t>44:07.063</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>5653216</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="94">
@@ -22534,34 +22530,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5158243</v>
+        <v>3105882</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Martin Chambers [sisu]</t>
+          <t>Tom Rose</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>JURASPORTS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>44:28.687</t>
+          <t>44:10.033</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="95">
@@ -22576,30 +22572,30 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5880054</v>
+        <v>5158243</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Kyle Sremaniak (SRT)</t>
+          <t>Martin Chambers [sisu]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>44:28.982</t>
+          <t>44:28.687</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>5653217</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="96">
@@ -22610,34 +22606,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>96834</v>
+        <v>5880054</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Marcus Illingworth (Evolve)</t>
+          <t>Kyle Sremaniak (SRT)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>EVOLVE</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>45:43.090</t>
+          <t>44:28.982</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>5653216</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="97">
@@ -22648,58 +22644,58 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1714</v>
+        <v>96834</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ALLI Craig Stiles (Dirt)</t>
+          <t>Marcus Illingworth (Evolve)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>EVOLVE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>01:03:26.156</t>
+          <t>45:43.090</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5653215</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3108682</v>
+        <v>1714</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Jonathan Ren&amp;eacute; [ Foudre]</t>
+          <t>ALLI Craig Stiles (Dirt)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -22709,11 +22705,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>42:30.202</t>
+          <t>01:03:26.156</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>5653214</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="99">
@@ -22728,26 +22724,26 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2297188</v>
+        <v>3108682</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Javier (HERC) </t>
+          <t>Jonathan Ren&amp;eacute; [ Foudre]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>42:40.849</t>
+          <t>42:30.202</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -22766,11 +22762,11 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3083458</v>
+        <v>2297188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Richard Emblen</t>
+          <t xml:space="preserve">3 Javier (HERC) </t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -22780,12 +22776,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>42:42.214</t>
+          <t>42:40.849</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -22800,30 +22796,30 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1285990</v>
+        <v>3083458</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Matthew Witney SPR</t>
+          <t>Richard Emblen</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>42:42.478</t>
+          <t>42:42.214</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -22838,30 +22834,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3161772</v>
+        <v>1285990</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Rafael Botte</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>Matthew Witney SPR</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>SPR</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>43:14.251</t>
+          <t>42:42.478</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>5653217</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="103">
@@ -22872,34 +22872,30 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1421189</v>
+        <v>3161772</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Michael Conley [ATP]</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ATP </t>
-        </is>
-      </c>
+          <t>Rafael Botte</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>43:17.607</t>
+          <t>43:14.251</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5653218</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="104">
@@ -22914,26 +22910,26 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5860485</v>
+        <v>1421189</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Fred  Bougie [Optimum]</t>
+          <t>Michael Conley [ATP]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Caf&amp;eacute; Champions</t>
+          <t xml:space="preserve">ATP </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>43:17.694</t>
+          <t>43:17.607</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -22948,30 +22944,30 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>112037</v>
+        <v>5860485</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Todd Graf BowHuntorDie</t>
+          <t>Fred  Bougie [Optimum]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UP!</t>
+          <t>Caf&amp;eacute; Champions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>43:19.381</t>
+          <t>43:17.694</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -22990,30 +22986,30 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1563175</v>
+        <v>112037</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Todd Graf BowHuntorDie</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>UP!</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>43:49.677</t>
+          <t>43:19.381</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="107">
@@ -23028,30 +23024,30 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5981378</v>
+        <v>1563175</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Chris Wooly [SRT]</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>S R T</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>43:57.447</t>
+          <t>43:49.677</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="108">
@@ -23066,30 +23062,30 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8033165</v>
+        <v>5981378</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Antonia  [RRC &amp;#128006;/HERC]</t>
+          <t>Chris Wooly [SRT]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>S R T</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>44:10.295</t>
+          <t>43:57.447</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>5653216</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="109">
@@ -23104,16 +23100,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6991072</v>
+        <v>8033165</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Antonia  [RRC &amp;#128006;/HERC]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -23123,11 +23119,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>44:17.630</t>
+          <t>44:10.295</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="110">
@@ -23142,16 +23138,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7424090</v>
+        <v>6991072</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Enric MM [HISP]</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HISP</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -23161,7 +23157,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>44:18.056</t>
+          <t>44:17.630</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -23176,30 +23172,34 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8442585</v>
+        <v>7424090</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Jakob Krejberg Bertelsen</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Enric MM [HISP]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>HISP</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>44:25.508</t>
+          <t>44:18.056</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="112">
@@ -23214,30 +23214,26 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2770378</v>
+        <v>8442585</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Patrick Bendix (D&amp;AElig;C)</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>D&amp;AElig;C</t>
-        </is>
-      </c>
+          <t>Jakob Krejberg Bertelsen</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>44:31.858</t>
+          <t>44:25.508</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5653217</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="113">
@@ -23248,30 +23244,34 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2457807</v>
+        <v>2770378</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sam Reid</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>Patrick Bendix (D&amp;AElig;C)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>D&amp;AElig;C</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>44:43.374</t>
+          <t>44:31.858</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>5653218</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="114">
@@ -23286,30 +23286,26 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2470325</v>
+        <v>2457807</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Richard Lutton</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NZBRO </t>
-        </is>
-      </c>
+          <t>Sam Reid</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>45:02.152</t>
+          <t>44:43.374</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="115">
@@ -23324,26 +23320,26 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>450573</v>
+        <v>2470325</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karin Lamers (HERC - SRT) </t>
+          <t>Richard Lutton</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">NZBRO </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>45:02.768</t>
+          <t>45:02.152</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -23362,26 +23358,26 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1640002</v>
+        <v>450573</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ryan Dagooc</t>
+          <t xml:space="preserve">Karin Lamers (HERC - SRT) </t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>45:02.936</t>
+          <t>45:02.768</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -23400,26 +23396,30 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5153366</v>
+        <v>1640002</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bernhard Gurra</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Ryan Dagooc</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>45:03.204</t>
+          <t>45:02.936</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>5653218</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="118">
@@ -23434,26 +23434,26 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>152268</v>
+        <v>5153366</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Peter Erichsen</t>
+          <t>Bernhard Gurra</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>45:06.666</t>
+          <t>45:03.204</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="119">
@@ -23464,30 +23464,30 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>7012651</v>
+        <v>152268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Alo&amp;iuml;s Lardinois</t>
+          <t>Peter Erichsen</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>45:11.179</t>
+          <t>45:06.666</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>5653216</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="120">
@@ -23498,30 +23498,30 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4795871</v>
+        <v>7012651</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Werner Nagels</t>
+          <t>Alo&amp;iuml;s Lardinois</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>45:26.791</t>
+          <t>45:11.179</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>5653215</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="121">
@@ -23536,22 +23536,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2360751</v>
+        <v>4795871</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Oliver Bartlett</t>
+          <t>Werner Nagels</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>45:28.242</t>
+          <t>45:26.791</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -23570,26 +23570,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6650098</v>
+        <v>2360751</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Kamil Maj</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+          <t>Oliver Bartlett</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>45:31.533</t>
+          <t>45:28.242</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -23608,11 +23604,11 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7821575</v>
+        <v>6650098</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Todd Arave</t>
+          <t>Kamil Maj</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -23627,11 +23623,11 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>45:51.238</t>
+          <t>45:31.533</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5653214</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="124">
@@ -23646,16 +23642,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>13655</v>
+        <v>7821575</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Craig Michie</t>
+          <t>Todd Arave</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -23665,11 +23661,11 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>45:59.864</t>
+          <t>45:51.238</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5653218</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="125">
@@ -23684,30 +23680,30 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5755052</v>
+        <v>13655</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Asger Fallesen (D&amp;AElig;C)</t>
+          <t>Craig Michie</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>D&amp;AElig;C</t>
+          <t>DIRT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>46:02.437</t>
+          <t>45:59.864</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>5653217</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="126">
@@ -23718,20 +23714,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2208223</v>
+        <v>5755052</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Marco Ferrario (SUGO&amp;#127813;)</t>
+          <t>Asger Fallesen (D&amp;AElig;C)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>D&amp;AElig;C</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -23741,11 +23737,11 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>46:03.037</t>
+          <t>46:02.437</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5653216</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="127">
@@ -23756,18 +23752,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7647313</v>
+        <v>2208223</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Bee Keeper</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>Marco Ferrario (SUGO&amp;#127813;)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -23775,11 +23775,11 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>46:16.038</t>
+          <t>46:03.037</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>5653218</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="128">
@@ -23794,18 +23794,14 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3990047</v>
+        <v>7647313</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Russell B (AHDR)</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Team AHDR</t>
-        </is>
-      </c>
+          <t>Bee Keeper</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -23813,11 +23809,11 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>46:35.691</t>
+          <t>46:16.038</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="129">
@@ -23832,26 +23828,26 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7853050</v>
+        <v>3990047</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>&amp;#9854; T&amp;auml;lyn [HERC] &amp;#127487;&amp;#127462;</t>
+          <t>Russell B (AHDR)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team AHDR</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>46:46.501</t>
+          <t>46:35.691</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -23866,15 +23862,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2692261</v>
+        <v>7853050</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>&amp;#9854; T&amp;auml;lyn [HERC] &amp;#127487;&amp;#127462;</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -23884,12 +23880,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>46:46.724</t>
+          <t>46:46.501</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -23904,34 +23900,34 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1598541</v>
+        <v>2692261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">steve pestridge GXY </t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[GALAXY]</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>47:35.493</t>
+          <t>46:46.724</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>5653216</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="132">
@@ -23946,30 +23942,30 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6928430</v>
+        <v>1598541</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>A lex A [ATGNI]</t>
+          <t xml:space="preserve">steve pestridge GXY </t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ATGNI</t>
+          <t>[GALAXY]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>47:38.427</t>
+          <t>47:35.493</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>5653217</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="133">
@@ -23984,30 +23980,30 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2053537</v>
+        <v>6928430</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Armand Ferro [ITA]</t>
+          <t>A lex A [ATGNI]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>47:42.829</t>
+          <t>47:38.427</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>5653215</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="134">
@@ -24018,30 +24014,34 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1024575</v>
+        <v>2053537</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Daniel M&amp;oslash;ller Buus</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Armand Ferro [ITA]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Team Italy</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>47:46.846</t>
+          <t>47:42.829</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>5653217</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="135">
@@ -24052,30 +24052,30 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8132260</v>
+        <v>1024575</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erik Straarup</t>
+          <t>Daniel M&amp;oslash;ller Buus</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>48:41.968</t>
+          <t>47:46.846</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5653214</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="136">
@@ -24090,26 +24090,22 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1820750</v>
+        <v>8132260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>PHILIPPE TINTIN</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>GCN_FR</t>
-        </is>
-      </c>
+          <t>Erik Straarup</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>70+</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>48:42.456</t>
+          <t>48:41.968</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -24128,30 +24124,30 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>5347091</v>
+        <v>1820750</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ted Smith (LightningV)</t>
+          <t>PHILIPPE TINTIN</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lightning Velo</t>
+          <t>GCN_FR</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>49:16.438</t>
+          <t>48:42.456</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5653218</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="138">
@@ -24162,20 +24158,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>581617</v>
+        <v>5347091</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>P Nilsson bef</t>
+          <t>Ted Smith (LightningV)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Befast </t>
+          <t>Lightning Velo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -24185,11 +24181,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>49:47.372</t>
+          <t>49:16.438</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>5653215</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="139">
@@ -24200,40 +24196,40 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1379058</v>
+        <v>581617</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t>P Nilsson bef</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t xml:space="preserve">Befast </t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>49:59.411</t>
+          <t>49:47.372</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>5653214</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -24242,26 +24238,30 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7481909</v>
+        <v>1379058</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Mathias Rask Dybvald (D&amp;AElig;C)</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>david white (HERC)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>44:58.933</t>
+          <t>49:59.411</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>5653217</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="141">
@@ -24276,30 +24276,26 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>243230</v>
+        <v>7481909</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Bram Bontje (Dirt)</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>Mathias Rask Dybvald (D&amp;AElig;C)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>45:01.317</t>
+          <t>44:58.933</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>5653218</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="142">
@@ -24314,26 +24310,30 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>7488477</v>
+        <v>243230</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R&amp;eacute;mi Lardinois</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>Bram Bontje (Dirt)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>46:02.958</t>
+          <t>45:01.317</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>5653216</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="143">
@@ -24348,30 +24348,26 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3089483</v>
+        <v>7488477</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Jonathan Hindle</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>R&amp;eacute;mi Lardinois</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>46:43.317</t>
+          <t>46:02.958</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="144">
@@ -24382,26 +24378,30 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1853682</v>
+        <v>3089483</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Jody Harvey</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>Jonathan Hindle</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>46:44.551</t>
+          <t>46:43.317</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -24420,30 +24420,26 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>4653373</v>
+        <v>1853682</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Paul Wa (HERC I)</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Jody Harvey</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>47:26.959</t>
+          <t>46:44.551</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>5653218</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="146">
@@ -24454,34 +24450,34 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1494540</v>
+        <v>4653373</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>D amo (WCC Kracken)</t>
+          <t>Paul Wa (HERC I)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>WCC</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>47:40.639</t>
+          <t>47:26.959</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>5653216</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="147">
@@ -24496,26 +24492,30 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4087374</v>
+        <v>1494540</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Christiaan Versteege</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>D amo (WCC Kracken)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>WCC</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>48:31.019</t>
+          <t>47:40.639</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>5653217</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="148">
@@ -24530,22 +24530,22 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7006151</v>
+        <v>4087374</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Marko Spudi&amp;#263;</t>
+          <t>Christiaan Versteege</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>48:31.260</t>
+          <t>48:31.019</t>
         </is>
       </c>
       <c r="H148" t="n">
@@ -24564,26 +24564,26 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6487938</v>
+        <v>7006151</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Julien Martel</t>
+          <t>Marko Spudi&amp;#263;</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>48:33.208</t>
+          <t>48:31.260</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>5653216</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="150">
@@ -24594,22 +24594,18 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1420129</v>
+        <v>6487938</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Vicente P.A 7490</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>PinoStoOG</t>
-        </is>
-      </c>
+          <t>Julien Martel</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -24617,11 +24613,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>48:59.786</t>
+          <t>48:33.208</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>5653214</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="151">
@@ -24636,26 +24632,26 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6547311</v>
+        <v>1420129</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
+          <t>Vicente P.A 7490</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>PinoStoOG</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>49:27.794</t>
+          <t>48:59.786</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -24674,11 +24670,11 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2648548</v>
+        <v>6547311</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Claire Greensides [HERC]</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -24688,12 +24684,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>49:28.157</t>
+          <t>49:27.794</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -24708,15 +24704,15 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>832585</v>
+        <v>2648548</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Claire Greensides [HERC]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -24726,12 +24722,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>49:28.384</t>
+          <t>49:28.157</t>
         </is>
       </c>
       <c r="H153" t="n">
@@ -24746,15 +24742,15 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>7438423</v>
+        <v>832585</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">M&amp;oacute;nica J. Gandarias [HERC] </t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -24769,7 +24765,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>50:00.492</t>
+          <t>49:28.384</t>
         </is>
       </c>
       <c r="H154" t="n">
@@ -24784,34 +24780,34 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2759649</v>
+        <v>7438423</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Loral Webster (ATP)</t>
+          <t xml:space="preserve">M&amp;oacute;nica J. Gandarias [HERC] </t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATP </t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>50:56.711</t>
+          <t>50:00.492</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>5653218</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="156">
@@ -24822,34 +24818,34 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>7424919</v>
+        <v>2759649</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erin Adams </t>
+          <t>Loral Webster (ATP)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Team AHDR</t>
+          <t xml:space="preserve">ATP </t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>50:57.388</t>
+          <t>50:56.711</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="157">
@@ -24864,26 +24860,30 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5180143</v>
+        <v>7424919</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Ross Stephen</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+          <t xml:space="preserve">Erin Adams </t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Team AHDR</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>51:16.468</t>
+          <t>50:57.388</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>5653217</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="158">
@@ -24894,30 +24894,30 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1295391</v>
+        <v>5180143</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Tatsuya Kawakami (TEAM Y)</t>
+          <t>Ross Stephen</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>51:31.055</t>
+          <t>51:16.468</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>5653214</v>
+        <v>5653217</v>
       </c>
     </row>
     <row r="159">
@@ -24932,26 +24932,26 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2799844</v>
+        <v>1295391</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>CAROL COLLYER</t>
+          <t>Tatsuya Kawakami (TEAM Y)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>51:47.583</t>
+          <t>51:31.055</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>5653218</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="160">
@@ -24966,30 +24966,26 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>946975</v>
+        <v>2799844</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Stuart Cook</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>DIRT</t>
-        </is>
-      </c>
+          <t>CAROL COLLYER</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>52:46.732</t>
+          <t>51:47.583</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>5653216</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="161">
@@ -25000,30 +24996,34 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>8151803</v>
+        <v>946975</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Mark Thomas</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>Stuart Cook</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>52:52.064</t>
+          <t>52:46.732</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>5653218</v>
+        <v>5653216</v>
       </c>
     </row>
     <row r="162">
@@ -25038,30 +25038,26 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4996569</v>
+        <v>8151803</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cathy Adams (AHDR Dynamos)</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Team AHDR</t>
-        </is>
-      </c>
+          <t>Mark Thomas</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>54:37.447</t>
+          <t>52:52.064</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>5653214</v>
+        <v>5653218</v>
       </c>
     </row>
     <row r="163">
@@ -25076,30 +25072,30 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>7529924</v>
+        <v>4996569</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Peter Whitelegg&amp;#129385;[HERC]</t>
+          <t>Cathy Adams (AHDR Dynamos)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team AHDR</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>57:23.659</t>
+          <t>54:37.447</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>5653215</v>
+        <v>5653214</v>
       </c>
     </row>
     <row r="164">
@@ -25114,14 +25110,18 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1835762</v>
+        <v>7529924</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>sergio  inostroza</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>Peter Whitelegg&amp;#129385;[HERC]</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
           <t>50+</t>
@@ -25129,48 +25129,82 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>01:11:51.644</t>
+          <t>57:23.659</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>5653216</v>
+        <v>5653215</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1835762</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>sergio  inostroza</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>01:11:51.644</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>5653216</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C165" t="n">
+      <c r="C166" t="n">
         <v>3837944</v>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>Demon Hunter (GTR) @YT &amp;#128121;&amp;#128692;</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>GTR</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>60+</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>01:18:34.386</t>
         </is>
       </c>
-      <c r="H165" t="n">
+      <c r="H166" t="n">
         <v>5653218</v>
       </c>
     </row>
